--- a/engstruct_casos.xlsx
+++ b/engstruct_casos.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,232 +429,232 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>cfg_ref_especie</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>cfg_ref_classe</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>cfg_ref_base</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>cfg_ref_vao_m</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Comprimento das longarinas (cm)</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Largura da pista disponível para longarinas (cm)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>['Circular']</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Tipo de seção do tabuleiro</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Carga permanente atuante no tabuleiro (kN/m²) excluso peso próprio (kPa)</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Carga por roda (kN) (kN)</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Carga de multidão (kN/m²) (kPa)</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Distância entre eixos (m) do veículo tipo (m)</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Classe de carregamento</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Classe de madeira</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Classe de umidade</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>γg - Carga permanente</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>γq - Carga variável</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>γwc - Cisalhamento</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>γwf - Flexão</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>ψ2</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Coeficiente para fluência Tabela 20 NBR 7190</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Percentual de robustez</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Densidade da madeira (kg/m³) da longarina (kg/m³)</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Resistência característica à flexão (MPa) da longarina (MPa)</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Resistência característica ao cisalhamento (MPa) da longarina (MPa)</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>Módulo de elasticidade à flexão (GPa) da longarina (GPa)</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Módulo de elasticidade médio à flexão (GPa) da longarina (GPa)</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Densidade da madeira (kg/m³) do tabuleiro (kg/m³)</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Resistência característica à flexão (MPa) do tabuleiro (MPa)</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>cfg_d_min</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>cfg_d_max</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>cfg_bw_min</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>cfg_bw_max</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>cfg_h_min</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>cfg_h_max</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>cfg_esp_long_min</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>cfg_esp_long_max</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>cfg_esp_tab_min</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>cfg_esp_tab_max</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>cfg_pop_size</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>cfg_n_gen</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>cfg_n_checagens</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>cfg_sobol</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>cfg_sobol_n_samples</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>cfg_ativo</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>cfg_subdiretorio</t>
         </is>
@@ -702,7 +714,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -714,7 +726,7 @@
         <v>3</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R2" t="n">
         <v>1.5</v>
@@ -729,7 +741,7 @@
         <v>0.3</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W2" t="n">
         <v>5</v>
@@ -856,7 +868,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -868,7 +880,7 @@
         <v>3</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R3" t="n">
         <v>1.5</v>
@@ -883,7 +895,7 @@
         <v>0.3</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W3" t="n">
         <v>5</v>
@@ -1010,7 +1022,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1022,7 +1034,7 @@
         <v>3</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R4" t="n">
         <v>1.5</v>
@@ -1037,7 +1049,7 @@
         <v>0.3</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W4" t="n">
         <v>5</v>
@@ -1164,7 +1176,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1176,7 +1188,7 @@
         <v>3</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R5" t="n">
         <v>1.5</v>
@@ -1191,7 +1203,7 @@
         <v>0.3</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W5" t="n">
         <v>5</v>
@@ -1318,7 +1330,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1330,7 +1342,7 @@
         <v>3</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R6" t="n">
         <v>1.5</v>
@@ -1345,7 +1357,7 @@
         <v>0.3</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W6" t="n">
         <v>5</v>
@@ -1472,7 +1484,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1484,7 +1496,7 @@
         <v>3</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R7" t="n">
         <v>1.5</v>
@@ -1499,7 +1511,7 @@
         <v>0.3</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W7" t="n">
         <v>5</v>
@@ -1626,7 +1638,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1638,7 +1650,7 @@
         <v>3</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R8" t="n">
         <v>1.5</v>
@@ -1653,7 +1665,7 @@
         <v>0.3</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W8" t="n">
         <v>5</v>
@@ -1780,7 +1792,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1792,7 +1804,7 @@
         <v>3</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R9" t="n">
         <v>1.5</v>
@@ -1807,7 +1819,7 @@
         <v>0.3</v>
       </c>
       <c r="V9" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W9" t="n">
         <v>5</v>
@@ -1934,7 +1946,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1946,7 +1958,7 @@
         <v>3</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R10" t="n">
         <v>1.5</v>
@@ -1961,7 +1973,7 @@
         <v>0.3</v>
       </c>
       <c r="V10" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W10" t="n">
         <v>5</v>
@@ -2088,7 +2100,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -2100,7 +2112,7 @@
         <v>3</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R11" t="n">
         <v>1.5</v>
@@ -2115,7 +2127,7 @@
         <v>0.3</v>
       </c>
       <c r="V11" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W11" t="n">
         <v>5</v>
@@ -2242,7 +2254,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -2254,7 +2266,7 @@
         <v>3</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R12" t="n">
         <v>1.5</v>
@@ -2269,7 +2281,7 @@
         <v>0.3</v>
       </c>
       <c r="V12" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W12" t="n">
         <v>5</v>
@@ -2396,7 +2408,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -2408,7 +2420,7 @@
         <v>3</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R13" t="n">
         <v>1.5</v>
@@ -2423,7 +2435,7 @@
         <v>0.3</v>
       </c>
       <c r="V13" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W13" t="n">
         <v>5</v>
@@ -2550,7 +2562,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -2562,7 +2574,7 @@
         <v>3</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R14" t="n">
         <v>1.5</v>
@@ -2577,7 +2589,7 @@
         <v>0.3</v>
       </c>
       <c r="V14" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W14" t="n">
         <v>5</v>
@@ -2704,7 +2716,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -2716,7 +2728,7 @@
         <v>3</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R15" t="n">
         <v>1.5</v>
@@ -2731,7 +2743,7 @@
         <v>0.3</v>
       </c>
       <c r="V15" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W15" t="n">
         <v>5</v>
@@ -2858,7 +2870,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -2870,7 +2882,7 @@
         <v>3</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R16" t="n">
         <v>1.5</v>
@@ -2885,7 +2897,7 @@
         <v>0.3</v>
       </c>
       <c r="V16" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W16" t="n">
         <v>5</v>
@@ -3012,7 +3024,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -3024,7 +3036,7 @@
         <v>3</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R17" t="n">
         <v>1.5</v>
@@ -3039,7 +3051,7 @@
         <v>0.3</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W17" t="n">
         <v>5</v>
@@ -3166,7 +3178,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -3178,7 +3190,7 @@
         <v>3</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R18" t="n">
         <v>1.5</v>
@@ -3193,7 +3205,7 @@
         <v>0.3</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W18" t="n">
         <v>5</v>
@@ -3320,7 +3332,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -3332,7 +3344,7 @@
         <v>3</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R19" t="n">
         <v>1.5</v>
@@ -3347,7 +3359,7 @@
         <v>0.3</v>
       </c>
       <c r="V19" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W19" t="n">
         <v>5</v>
@@ -3474,7 +3486,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -3486,7 +3498,7 @@
         <v>3</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R20" t="n">
         <v>1.5</v>
@@ -3501,7 +3513,7 @@
         <v>0.3</v>
       </c>
       <c r="V20" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W20" t="n">
         <v>5</v>
@@ -3628,7 +3640,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -3640,7 +3652,7 @@
         <v>3</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R21" t="n">
         <v>1.5</v>
@@ -3655,7 +3667,7 @@
         <v>0.3</v>
       </c>
       <c r="V21" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W21" t="n">
         <v>5</v>
@@ -3782,7 +3794,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -3794,7 +3806,7 @@
         <v>3</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R22" t="n">
         <v>1.5</v>
@@ -3809,7 +3821,7 @@
         <v>0.3</v>
       </c>
       <c r="V22" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W22" t="n">
         <v>5</v>
@@ -3936,7 +3948,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -3948,7 +3960,7 @@
         <v>3</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R23" t="n">
         <v>1.5</v>
@@ -3963,7 +3975,7 @@
         <v>0.3</v>
       </c>
       <c r="V23" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W23" t="n">
         <v>5</v>
@@ -4090,7 +4102,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -4102,7 +4114,7 @@
         <v>3</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R24" t="n">
         <v>1.5</v>
@@ -4117,7 +4129,7 @@
         <v>0.3</v>
       </c>
       <c r="V24" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W24" t="n">
         <v>5</v>
@@ -4244,7 +4256,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -4256,7 +4268,7 @@
         <v>3</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R25" t="n">
         <v>1.5</v>
@@ -4271,7 +4283,7 @@
         <v>0.3</v>
       </c>
       <c r="V25" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W25" t="n">
         <v>5</v>
@@ -4398,7 +4410,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -4410,7 +4422,7 @@
         <v>3</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R26" t="n">
         <v>1.5</v>
@@ -4425,7 +4437,7 @@
         <v>0.3</v>
       </c>
       <c r="V26" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W26" t="n">
         <v>5</v>
@@ -4552,7 +4564,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -4564,7 +4576,7 @@
         <v>3</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R27" t="n">
         <v>1.5</v>
@@ -4579,7 +4591,7 @@
         <v>0.3</v>
       </c>
       <c r="V27" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W27" t="n">
         <v>5</v>
@@ -4706,7 +4718,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -4718,7 +4730,7 @@
         <v>3</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R28" t="n">
         <v>1.5</v>
@@ -4733,7 +4745,7 @@
         <v>0.3</v>
       </c>
       <c r="V28" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W28" t="n">
         <v>5</v>
@@ -4860,7 +4872,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -4872,7 +4884,7 @@
         <v>3</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R29" t="n">
         <v>1.5</v>
@@ -4887,7 +4899,7 @@
         <v>0.3</v>
       </c>
       <c r="V29" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W29" t="n">
         <v>5</v>
@@ -5014,7 +5026,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -5026,7 +5038,7 @@
         <v>3</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R30" t="n">
         <v>1.5</v>
@@ -5041,7 +5053,7 @@
         <v>0.3</v>
       </c>
       <c r="V30" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W30" t="n">
         <v>5</v>
@@ -5168,7 +5180,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -5180,7 +5192,7 @@
         <v>3</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R31" t="n">
         <v>1.5</v>
@@ -5195,7 +5207,7 @@
         <v>0.3</v>
       </c>
       <c r="V31" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W31" t="n">
         <v>5</v>
@@ -5322,7 +5334,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -5334,7 +5346,7 @@
         <v>3</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R32" t="n">
         <v>1.5</v>
@@ -5349,7 +5361,7 @@
         <v>0.3</v>
       </c>
       <c r="V32" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W32" t="n">
         <v>5</v>
@@ -5476,7 +5488,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -5488,7 +5500,7 @@
         <v>3</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R33" t="n">
         <v>1.5</v>
@@ -5503,7 +5515,7 @@
         <v>0.3</v>
       </c>
       <c r="V33" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W33" t="n">
         <v>5</v>
@@ -5630,7 +5642,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -5642,7 +5654,7 @@
         <v>3</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R34" t="n">
         <v>1.5</v>
@@ -5657,7 +5669,7 @@
         <v>0.3</v>
       </c>
       <c r="V34" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W34" t="n">
         <v>5</v>
@@ -5784,7 +5796,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -5796,7 +5808,7 @@
         <v>3</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R35" t="n">
         <v>1.5</v>
@@ -5811,7 +5823,7 @@
         <v>0.3</v>
       </c>
       <c r="V35" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W35" t="n">
         <v>5</v>
@@ -5938,7 +5950,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -5950,7 +5962,7 @@
         <v>3</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R36" t="n">
         <v>1.5</v>
@@ -5965,7 +5977,7 @@
         <v>0.3</v>
       </c>
       <c r="V36" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W36" t="n">
         <v>5</v>
@@ -6092,7 +6104,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -6104,7 +6116,7 @@
         <v>3</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R37" t="n">
         <v>1.5</v>
@@ -6119,7 +6131,7 @@
         <v>0.3</v>
       </c>
       <c r="V37" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W37" t="n">
         <v>5</v>
@@ -6246,7 +6258,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -6258,7 +6270,7 @@
         <v>3</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R38" t="n">
         <v>1.5</v>
@@ -6273,7 +6285,7 @@
         <v>0.3</v>
       </c>
       <c r="V38" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W38" t="n">
         <v>5</v>
@@ -6400,7 +6412,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -6412,7 +6424,7 @@
         <v>3</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R39" t="n">
         <v>1.5</v>
@@ -6427,7 +6439,7 @@
         <v>0.3</v>
       </c>
       <c r="V39" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W39" t="n">
         <v>5</v>
@@ -6554,7 +6566,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -6566,7 +6578,7 @@
         <v>3</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R40" t="n">
         <v>1.5</v>
@@ -6581,7 +6593,7 @@
         <v>0.3</v>
       </c>
       <c r="V40" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W40" t="n">
         <v>5</v>
@@ -6708,7 +6720,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -6720,7 +6732,7 @@
         <v>3</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R41" t="n">
         <v>1.5</v>
@@ -6735,7 +6747,7 @@
         <v>0.3</v>
       </c>
       <c r="V41" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W41" t="n">
         <v>5</v>
@@ -6862,7 +6874,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -6874,7 +6886,7 @@
         <v>3</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R42" t="n">
         <v>1.5</v>
@@ -6889,7 +6901,7 @@
         <v>0.3</v>
       </c>
       <c r="V42" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W42" t="n">
         <v>5</v>
@@ -7016,7 +7028,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -7028,7 +7040,7 @@
         <v>3</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R43" t="n">
         <v>1.5</v>
@@ -7043,7 +7055,7 @@
         <v>0.3</v>
       </c>
       <c r="V43" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W43" t="n">
         <v>5</v>
@@ -7170,7 +7182,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -7182,7 +7194,7 @@
         <v>3</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R44" t="n">
         <v>1.5</v>
@@ -7197,7 +7209,7 @@
         <v>0.3</v>
       </c>
       <c r="V44" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W44" t="n">
         <v>5</v>
@@ -7324,7 +7336,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -7336,7 +7348,7 @@
         <v>3</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R45" t="n">
         <v>1.5</v>
@@ -7351,7 +7363,7 @@
         <v>0.3</v>
       </c>
       <c r="V45" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W45" t="n">
         <v>5</v>
@@ -7478,7 +7490,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -7490,7 +7502,7 @@
         <v>3</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R46" t="n">
         <v>1.5</v>
@@ -7505,7 +7517,7 @@
         <v>0.3</v>
       </c>
       <c r="V46" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W46" t="n">
         <v>5</v>
@@ -7632,7 +7644,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -7644,7 +7656,7 @@
         <v>3</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R47" t="n">
         <v>1.5</v>
@@ -7659,7 +7671,7 @@
         <v>0.3</v>
       </c>
       <c r="V47" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W47" t="n">
         <v>5</v>
@@ -7786,7 +7798,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -7798,7 +7810,7 @@
         <v>3</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R48" t="n">
         <v>1.5</v>
@@ -7813,7 +7825,7 @@
         <v>0.3</v>
       </c>
       <c r="V48" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W48" t="n">
         <v>5</v>
@@ -7940,7 +7952,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -7952,7 +7964,7 @@
         <v>3</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R49" t="n">
         <v>1.5</v>
@@ -7967,7 +7979,7 @@
         <v>0.3</v>
       </c>
       <c r="V49" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W49" t="n">
         <v>5</v>
@@ -8094,7 +8106,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -8106,7 +8118,7 @@
         <v>3</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R50" t="n">
         <v>1.5</v>
@@ -8121,7 +8133,7 @@
         <v>0.3</v>
       </c>
       <c r="V50" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W50" t="n">
         <v>5</v>
@@ -8248,7 +8260,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -8260,7 +8272,7 @@
         <v>3</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R51" t="n">
         <v>1.5</v>
@@ -8275,7 +8287,7 @@
         <v>0.3</v>
       </c>
       <c r="V51" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W51" t="n">
         <v>5</v>
@@ -8402,7 +8414,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -8414,7 +8426,7 @@
         <v>3</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R52" t="n">
         <v>1.5</v>
@@ -8429,7 +8441,7 @@
         <v>0.3</v>
       </c>
       <c r="V52" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W52" t="n">
         <v>5</v>
@@ -8556,7 +8568,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -8568,7 +8580,7 @@
         <v>3</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R53" t="n">
         <v>1.5</v>
@@ -8583,7 +8595,7 @@
         <v>0.3</v>
       </c>
       <c r="V53" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W53" t="n">
         <v>5</v>
@@ -8710,7 +8722,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -8722,7 +8734,7 @@
         <v>3</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R54" t="n">
         <v>1.5</v>
@@ -8737,7 +8749,7 @@
         <v>0.3</v>
       </c>
       <c r="V54" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W54" t="n">
         <v>5</v>
@@ -8864,7 +8876,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -8876,7 +8888,7 @@
         <v>3</v>
       </c>
       <c r="Q55" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R55" t="n">
         <v>1.5</v>
@@ -8891,7 +8903,7 @@
         <v>0.3</v>
       </c>
       <c r="V55" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W55" t="n">
         <v>5</v>
@@ -9018,7 +9030,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -9030,7 +9042,7 @@
         <v>3</v>
       </c>
       <c r="Q56" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R56" t="n">
         <v>1.5</v>
@@ -9045,7 +9057,7 @@
         <v>0.3</v>
       </c>
       <c r="V56" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W56" t="n">
         <v>5</v>
@@ -9172,7 +9184,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -9184,7 +9196,7 @@
         <v>3</v>
       </c>
       <c r="Q57" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R57" t="n">
         <v>1.5</v>
@@ -9199,7 +9211,7 @@
         <v>0.3</v>
       </c>
       <c r="V57" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W57" t="n">
         <v>5</v>
@@ -9326,7 +9338,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -9338,7 +9350,7 @@
         <v>3</v>
       </c>
       <c r="Q58" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R58" t="n">
         <v>1.5</v>
@@ -9353,7 +9365,7 @@
         <v>0.3</v>
       </c>
       <c r="V58" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W58" t="n">
         <v>5</v>
@@ -9480,7 +9492,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -9492,7 +9504,7 @@
         <v>3</v>
       </c>
       <c r="Q59" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R59" t="n">
         <v>1.5</v>
@@ -9507,7 +9519,7 @@
         <v>0.3</v>
       </c>
       <c r="V59" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W59" t="n">
         <v>5</v>
@@ -9634,7 +9646,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -9646,7 +9658,7 @@
         <v>3</v>
       </c>
       <c r="Q60" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R60" t="n">
         <v>1.5</v>
@@ -9661,7 +9673,7 @@
         <v>0.3</v>
       </c>
       <c r="V60" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W60" t="n">
         <v>5</v>
@@ -9788,7 +9800,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -9800,7 +9812,7 @@
         <v>3</v>
       </c>
       <c r="Q61" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R61" t="n">
         <v>1.5</v>
@@ -9815,7 +9827,7 @@
         <v>0.3</v>
       </c>
       <c r="V61" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W61" t="n">
         <v>5</v>
@@ -9942,7 +9954,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -9954,7 +9966,7 @@
         <v>3</v>
       </c>
       <c r="Q62" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R62" t="n">
         <v>1.5</v>
@@ -9969,7 +9981,7 @@
         <v>0.3</v>
       </c>
       <c r="V62" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W62" t="n">
         <v>5</v>
@@ -10096,7 +10108,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -10108,7 +10120,7 @@
         <v>3</v>
       </c>
       <c r="Q63" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R63" t="n">
         <v>1.5</v>
@@ -10123,7 +10135,7 @@
         <v>0.3</v>
       </c>
       <c r="V63" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W63" t="n">
         <v>5</v>
@@ -10250,7 +10262,7 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -10262,7 +10274,7 @@
         <v>3</v>
       </c>
       <c r="Q64" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R64" t="n">
         <v>1.5</v>
@@ -10277,7 +10289,7 @@
         <v>0.3</v>
       </c>
       <c r="V64" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W64" t="n">
         <v>5</v>
@@ -10404,7 +10416,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -10416,7 +10428,7 @@
         <v>3</v>
       </c>
       <c r="Q65" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R65" t="n">
         <v>1.5</v>
@@ -10431,7 +10443,7 @@
         <v>0.3</v>
       </c>
       <c r="V65" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W65" t="n">
         <v>5</v>
@@ -10558,7 +10570,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -10570,7 +10582,7 @@
         <v>3</v>
       </c>
       <c r="Q66" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R66" t="n">
         <v>1.5</v>
@@ -10585,7 +10597,7 @@
         <v>0.3</v>
       </c>
       <c r="V66" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W66" t="n">
         <v>5</v>
@@ -10712,7 +10724,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -10724,7 +10736,7 @@
         <v>3</v>
       </c>
       <c r="Q67" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R67" t="n">
         <v>1.5</v>
@@ -10739,7 +10751,7 @@
         <v>0.3</v>
       </c>
       <c r="V67" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W67" t="n">
         <v>5</v>
@@ -10866,7 +10878,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -10878,7 +10890,7 @@
         <v>3</v>
       </c>
       <c r="Q68" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R68" t="n">
         <v>1.5</v>
@@ -10893,7 +10905,7 @@
         <v>0.3</v>
       </c>
       <c r="V68" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W68" t="n">
         <v>5</v>
@@ -11020,7 +11032,7 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -11032,7 +11044,7 @@
         <v>3</v>
       </c>
       <c r="Q69" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R69" t="n">
         <v>1.5</v>
@@ -11047,7 +11059,7 @@
         <v>0.3</v>
       </c>
       <c r="V69" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W69" t="n">
         <v>5</v>
@@ -11174,7 +11186,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -11186,7 +11198,7 @@
         <v>3</v>
       </c>
       <c r="Q70" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R70" t="n">
         <v>1.5</v>
@@ -11201,7 +11213,7 @@
         <v>0.3</v>
       </c>
       <c r="V70" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W70" t="n">
         <v>5</v>
@@ -11328,7 +11340,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -11340,7 +11352,7 @@
         <v>3</v>
       </c>
       <c r="Q71" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R71" t="n">
         <v>1.5</v>
@@ -11355,7 +11367,7 @@
         <v>0.3</v>
       </c>
       <c r="V71" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W71" t="n">
         <v>5</v>
@@ -11482,7 +11494,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -11494,7 +11506,7 @@
         <v>3</v>
       </c>
       <c r="Q72" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R72" t="n">
         <v>1.5</v>
@@ -11509,7 +11521,7 @@
         <v>0.3</v>
       </c>
       <c r="V72" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W72" t="n">
         <v>5</v>
@@ -11636,7 +11648,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -11648,7 +11660,7 @@
         <v>3</v>
       </c>
       <c r="Q73" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R73" t="n">
         <v>1.5</v>
@@ -11663,7 +11675,7 @@
         <v>0.3</v>
       </c>
       <c r="V73" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W73" t="n">
         <v>5</v>
@@ -11790,7 +11802,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -11802,7 +11814,7 @@
         <v>3</v>
       </c>
       <c r="Q74" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R74" t="n">
         <v>1.5</v>
@@ -11817,7 +11829,7 @@
         <v>0.3</v>
       </c>
       <c r="V74" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W74" t="n">
         <v>5</v>
@@ -11944,7 +11956,7 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -11956,7 +11968,7 @@
         <v>3</v>
       </c>
       <c r="Q75" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R75" t="n">
         <v>1.5</v>
@@ -11971,7 +11983,7 @@
         <v>0.3</v>
       </c>
       <c r="V75" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W75" t="n">
         <v>5</v>
@@ -12098,7 +12110,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -12110,7 +12122,7 @@
         <v>3</v>
       </c>
       <c r="Q76" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R76" t="n">
         <v>1.5</v>
@@ -12125,7 +12137,7 @@
         <v>0.3</v>
       </c>
       <c r="V76" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W76" t="n">
         <v>5</v>
@@ -12252,7 +12264,7 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -12264,7 +12276,7 @@
         <v>3</v>
       </c>
       <c r="Q77" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R77" t="n">
         <v>1.5</v>
@@ -12279,7 +12291,7 @@
         <v>0.3</v>
       </c>
       <c r="V77" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W77" t="n">
         <v>5</v>
@@ -12406,7 +12418,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -12418,7 +12430,7 @@
         <v>3</v>
       </c>
       <c r="Q78" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R78" t="n">
         <v>1.5</v>
@@ -12433,7 +12445,7 @@
         <v>0.3</v>
       </c>
       <c r="V78" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W78" t="n">
         <v>5</v>
@@ -12560,7 +12572,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
@@ -12572,7 +12584,7 @@
         <v>3</v>
       </c>
       <c r="Q79" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R79" t="n">
         <v>1.5</v>
@@ -12587,7 +12599,7 @@
         <v>0.3</v>
       </c>
       <c r="V79" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W79" t="n">
         <v>5</v>
@@ -12714,7 +12726,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
@@ -12726,7 +12738,7 @@
         <v>3</v>
       </c>
       <c r="Q80" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R80" t="n">
         <v>1.5</v>
@@ -12741,7 +12753,7 @@
         <v>0.3</v>
       </c>
       <c r="V80" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W80" t="n">
         <v>5</v>
@@ -12868,7 +12880,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
@@ -12880,7 +12892,7 @@
         <v>3</v>
       </c>
       <c r="Q81" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R81" t="n">
         <v>1.5</v>
@@ -12895,7 +12907,7 @@
         <v>0.3</v>
       </c>
       <c r="V81" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W81" t="n">
         <v>5</v>
@@ -13022,7 +13034,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
@@ -13034,7 +13046,7 @@
         <v>3</v>
       </c>
       <c r="Q82" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R82" t="n">
         <v>1.5</v>
@@ -13049,7 +13061,7 @@
         <v>0.3</v>
       </c>
       <c r="V82" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W82" t="n">
         <v>5</v>
@@ -13176,7 +13188,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -13188,7 +13200,7 @@
         <v>3</v>
       </c>
       <c r="Q83" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R83" t="n">
         <v>1.5</v>
@@ -13203,7 +13215,7 @@
         <v>0.3</v>
       </c>
       <c r="V83" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W83" t="n">
         <v>5</v>
@@ -13330,7 +13342,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
@@ -13342,7 +13354,7 @@
         <v>3</v>
       </c>
       <c r="Q84" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R84" t="n">
         <v>1.5</v>
@@ -13357,7 +13369,7 @@
         <v>0.3</v>
       </c>
       <c r="V84" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W84" t="n">
         <v>5</v>
@@ -13484,7 +13496,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
@@ -13496,7 +13508,7 @@
         <v>3</v>
       </c>
       <c r="Q85" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R85" t="n">
         <v>1.5</v>
@@ -13511,7 +13523,7 @@
         <v>0.3</v>
       </c>
       <c r="V85" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W85" t="n">
         <v>5</v>
@@ -13638,7 +13650,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
@@ -13650,7 +13662,7 @@
         <v>3</v>
       </c>
       <c r="Q86" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R86" t="n">
         <v>1.5</v>
@@ -13665,7 +13677,7 @@
         <v>0.3</v>
       </c>
       <c r="V86" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W86" t="n">
         <v>5</v>
@@ -13792,7 +13804,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
@@ -13804,7 +13816,7 @@
         <v>3</v>
       </c>
       <c r="Q87" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R87" t="n">
         <v>1.5</v>
@@ -13819,7 +13831,7 @@
         <v>0.3</v>
       </c>
       <c r="V87" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W87" t="n">
         <v>5</v>
@@ -13946,7 +13958,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
@@ -13958,7 +13970,7 @@
         <v>3</v>
       </c>
       <c r="Q88" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R88" t="n">
         <v>1.5</v>
@@ -13973,7 +13985,7 @@
         <v>0.3</v>
       </c>
       <c r="V88" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W88" t="n">
         <v>5</v>
@@ -14100,7 +14112,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
@@ -14112,7 +14124,7 @@
         <v>3</v>
       </c>
       <c r="Q89" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R89" t="n">
         <v>1.5</v>
@@ -14127,7 +14139,7 @@
         <v>0.3</v>
       </c>
       <c r="V89" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W89" t="n">
         <v>5</v>
@@ -14254,7 +14266,7 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
@@ -14266,7 +14278,7 @@
         <v>3</v>
       </c>
       <c r="Q90" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R90" t="n">
         <v>1.5</v>
@@ -14281,7 +14293,7 @@
         <v>0.3</v>
       </c>
       <c r="V90" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W90" t="n">
         <v>5</v>
@@ -14408,7 +14420,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
@@ -14420,7 +14432,7 @@
         <v>3</v>
       </c>
       <c r="Q91" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R91" t="n">
         <v>1.5</v>
@@ -14435,7 +14447,7 @@
         <v>0.3</v>
       </c>
       <c r="V91" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W91" t="n">
         <v>5</v>
@@ -14562,7 +14574,7 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
@@ -14574,7 +14586,7 @@
         <v>3</v>
       </c>
       <c r="Q92" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R92" t="n">
         <v>1.5</v>
@@ -14589,7 +14601,7 @@
         <v>0.3</v>
       </c>
       <c r="V92" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W92" t="n">
         <v>5</v>
@@ -14716,7 +14728,7 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
@@ -14728,7 +14740,7 @@
         <v>3</v>
       </c>
       <c r="Q93" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R93" t="n">
         <v>1.5</v>
@@ -14743,7 +14755,7 @@
         <v>0.3</v>
       </c>
       <c r="V93" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W93" t="n">
         <v>5</v>
@@ -14870,7 +14882,7 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
@@ -14882,7 +14894,7 @@
         <v>3</v>
       </c>
       <c r="Q94" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R94" t="n">
         <v>1.5</v>
@@ -14897,7 +14909,7 @@
         <v>0.3</v>
       </c>
       <c r="V94" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W94" t="n">
         <v>5</v>
@@ -15024,7 +15036,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
@@ -15036,7 +15048,7 @@
         <v>3</v>
       </c>
       <c r="Q95" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R95" t="n">
         <v>1.5</v>
@@ -15051,7 +15063,7 @@
         <v>0.3</v>
       </c>
       <c r="V95" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W95" t="n">
         <v>5</v>
@@ -15178,7 +15190,7 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
@@ -15190,7 +15202,7 @@
         <v>3</v>
       </c>
       <c r="Q96" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R96" t="n">
         <v>1.5</v>
@@ -15205,7 +15217,7 @@
         <v>0.3</v>
       </c>
       <c r="V96" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W96" t="n">
         <v>5</v>
@@ -15332,7 +15344,7 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
@@ -15344,7 +15356,7 @@
         <v>3</v>
       </c>
       <c r="Q97" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R97" t="n">
         <v>1.5</v>
@@ -15359,7 +15371,7 @@
         <v>0.3</v>
       </c>
       <c r="V97" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W97" t="n">
         <v>5</v>
@@ -15486,7 +15498,7 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
@@ -15498,7 +15510,7 @@
         <v>3</v>
       </c>
       <c r="Q98" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R98" t="n">
         <v>1.5</v>
@@ -15513,7 +15525,7 @@
         <v>0.3</v>
       </c>
       <c r="V98" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W98" t="n">
         <v>5</v>
@@ -15640,7 +15652,7 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
@@ -15652,7 +15664,7 @@
         <v>3</v>
       </c>
       <c r="Q99" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R99" t="n">
         <v>1.5</v>
@@ -15667,7 +15679,7 @@
         <v>0.3</v>
       </c>
       <c r="V99" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W99" t="n">
         <v>5</v>
@@ -15794,7 +15806,7 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
@@ -15806,7 +15818,7 @@
         <v>3</v>
       </c>
       <c r="Q100" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R100" t="n">
         <v>1.5</v>
@@ -15821,7 +15833,7 @@
         <v>0.3</v>
       </c>
       <c r="V100" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W100" t="n">
         <v>5</v>
@@ -15948,7 +15960,7 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
@@ -15960,7 +15972,7 @@
         <v>3</v>
       </c>
       <c r="Q101" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R101" t="n">
         <v>1.5</v>
@@ -15975,7 +15987,7 @@
         <v>0.3</v>
       </c>
       <c r="V101" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W101" t="n">
         <v>5</v>
@@ -16102,7 +16114,7 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
@@ -16114,7 +16126,7 @@
         <v>3</v>
       </c>
       <c r="Q102" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R102" t="n">
         <v>1.5</v>
@@ -16129,7 +16141,7 @@
         <v>0.3</v>
       </c>
       <c r="V102" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W102" t="n">
         <v>5</v>
@@ -16256,7 +16268,7 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
@@ -16268,7 +16280,7 @@
         <v>3</v>
       </c>
       <c r="Q103" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R103" t="n">
         <v>1.5</v>
@@ -16283,7 +16295,7 @@
         <v>0.3</v>
       </c>
       <c r="V103" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W103" t="n">
         <v>5</v>
@@ -16410,7 +16422,7 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
@@ -16422,7 +16434,7 @@
         <v>3</v>
       </c>
       <c r="Q104" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R104" t="n">
         <v>1.5</v>
@@ -16437,7 +16449,7 @@
         <v>0.3</v>
       </c>
       <c r="V104" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W104" t="n">
         <v>5</v>
@@ -16564,7 +16576,7 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
@@ -16576,7 +16588,7 @@
         <v>3</v>
       </c>
       <c r="Q105" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R105" t="n">
         <v>1.5</v>
@@ -16591,7 +16603,7 @@
         <v>0.3</v>
       </c>
       <c r="V105" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W105" t="n">
         <v>5</v>
@@ -16718,7 +16730,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
@@ -16730,7 +16742,7 @@
         <v>3</v>
       </c>
       <c r="Q106" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R106" t="n">
         <v>1.5</v>
@@ -16745,7 +16757,7 @@
         <v>0.3</v>
       </c>
       <c r="V106" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W106" t="n">
         <v>5</v>
@@ -16872,7 +16884,7 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
@@ -16884,7 +16896,7 @@
         <v>3</v>
       </c>
       <c r="Q107" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R107" t="n">
         <v>1.5</v>
@@ -16899,7 +16911,7 @@
         <v>0.3</v>
       </c>
       <c r="V107" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W107" t="n">
         <v>5</v>
@@ -17026,7 +17038,7 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O108" t="inlineStr">
@@ -17038,7 +17050,7 @@
         <v>3</v>
       </c>
       <c r="Q108" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R108" t="n">
         <v>1.5</v>
@@ -17053,7 +17065,7 @@
         <v>0.3</v>
       </c>
       <c r="V108" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W108" t="n">
         <v>5</v>
@@ -17180,7 +17192,7 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O109" t="inlineStr">
@@ -17192,7 +17204,7 @@
         <v>3</v>
       </c>
       <c r="Q109" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R109" t="n">
         <v>1.5</v>
@@ -17207,7 +17219,7 @@
         <v>0.3</v>
       </c>
       <c r="V109" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W109" t="n">
         <v>5</v>
@@ -17334,7 +17346,7 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
@@ -17346,7 +17358,7 @@
         <v>3</v>
       </c>
       <c r="Q110" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R110" t="n">
         <v>1.5</v>
@@ -17361,7 +17373,7 @@
         <v>0.3</v>
       </c>
       <c r="V110" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W110" t="n">
         <v>5</v>
@@ -17488,7 +17500,7 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O111" t="inlineStr">
@@ -17500,7 +17512,7 @@
         <v>3</v>
       </c>
       <c r="Q111" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R111" t="n">
         <v>1.5</v>
@@ -17515,7 +17527,7 @@
         <v>0.3</v>
       </c>
       <c r="V111" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W111" t="n">
         <v>5</v>
@@ -17642,7 +17654,7 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O112" t="inlineStr">
@@ -17654,7 +17666,7 @@
         <v>3</v>
       </c>
       <c r="Q112" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R112" t="n">
         <v>1.5</v>
@@ -17669,7 +17681,7 @@
         <v>0.3</v>
       </c>
       <c r="V112" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W112" t="n">
         <v>5</v>
@@ -17796,7 +17808,7 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
@@ -17808,7 +17820,7 @@
         <v>3</v>
       </c>
       <c r="Q113" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R113" t="n">
         <v>1.5</v>
@@ -17823,7 +17835,7 @@
         <v>0.3</v>
       </c>
       <c r="V113" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W113" t="n">
         <v>5</v>
@@ -17950,7 +17962,7 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O114" t="inlineStr">
@@ -17962,7 +17974,7 @@
         <v>3</v>
       </c>
       <c r="Q114" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R114" t="n">
         <v>1.5</v>
@@ -17977,7 +17989,7 @@
         <v>0.3</v>
       </c>
       <c r="V114" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W114" t="n">
         <v>5</v>
@@ -18104,7 +18116,7 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
@@ -18116,7 +18128,7 @@
         <v>3</v>
       </c>
       <c r="Q115" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R115" t="n">
         <v>1.5</v>
@@ -18131,7 +18143,7 @@
         <v>0.3</v>
       </c>
       <c r="V115" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W115" t="n">
         <v>5</v>
@@ -18258,7 +18270,7 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O116" t="inlineStr">
@@ -18270,7 +18282,7 @@
         <v>3</v>
       </c>
       <c r="Q116" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R116" t="n">
         <v>1.5</v>
@@ -18285,7 +18297,7 @@
         <v>0.3</v>
       </c>
       <c r="V116" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W116" t="n">
         <v>5</v>
@@ -18412,7 +18424,7 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O117" t="inlineStr">
@@ -18424,7 +18436,7 @@
         <v>3</v>
       </c>
       <c r="Q117" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R117" t="n">
         <v>1.5</v>
@@ -18439,7 +18451,7 @@
         <v>0.3</v>
       </c>
       <c r="V117" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W117" t="n">
         <v>5</v>
@@ -18566,7 +18578,7 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O118" t="inlineStr">
@@ -18578,7 +18590,7 @@
         <v>3</v>
       </c>
       <c r="Q118" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R118" t="n">
         <v>1.5</v>
@@ -18593,7 +18605,7 @@
         <v>0.3</v>
       </c>
       <c r="V118" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W118" t="n">
         <v>5</v>
@@ -18720,7 +18732,7 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O119" t="inlineStr">
@@ -18732,7 +18744,7 @@
         <v>3</v>
       </c>
       <c r="Q119" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R119" t="n">
         <v>1.5</v>
@@ -18747,7 +18759,7 @@
         <v>0.3</v>
       </c>
       <c r="V119" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W119" t="n">
         <v>5</v>
@@ -18874,7 +18886,7 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O120" t="inlineStr">
@@ -18886,7 +18898,7 @@
         <v>3</v>
       </c>
       <c r="Q120" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R120" t="n">
         <v>1.5</v>
@@ -18901,7 +18913,7 @@
         <v>0.3</v>
       </c>
       <c r="V120" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W120" t="n">
         <v>5</v>
@@ -19028,7 +19040,7 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O121" t="inlineStr">
@@ -19040,7 +19052,7 @@
         <v>3</v>
       </c>
       <c r="Q121" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R121" t="n">
         <v>1.5</v>
@@ -19055,7 +19067,7 @@
         <v>0.3</v>
       </c>
       <c r="V121" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W121" t="n">
         <v>5</v>
@@ -19182,7 +19194,7 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O122" t="inlineStr">
@@ -19194,7 +19206,7 @@
         <v>3</v>
       </c>
       <c r="Q122" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R122" t="n">
         <v>1.5</v>
@@ -19209,7 +19221,7 @@
         <v>0.3</v>
       </c>
       <c r="V122" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W122" t="n">
         <v>5</v>
@@ -19336,7 +19348,7 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O123" t="inlineStr">
@@ -19348,7 +19360,7 @@
         <v>3</v>
       </c>
       <c r="Q123" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R123" t="n">
         <v>1.5</v>
@@ -19363,7 +19375,7 @@
         <v>0.3</v>
       </c>
       <c r="V123" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W123" t="n">
         <v>5</v>
@@ -19490,7 +19502,7 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O124" t="inlineStr">
@@ -19502,7 +19514,7 @@
         <v>3</v>
       </c>
       <c r="Q124" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R124" t="n">
         <v>1.5</v>
@@ -19517,7 +19529,7 @@
         <v>0.3</v>
       </c>
       <c r="V124" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W124" t="n">
         <v>5</v>
@@ -19644,7 +19656,7 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O125" t="inlineStr">
@@ -19656,7 +19668,7 @@
         <v>3</v>
       </c>
       <c r="Q125" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R125" t="n">
         <v>1.5</v>
@@ -19671,7 +19683,7 @@
         <v>0.3</v>
       </c>
       <c r="V125" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W125" t="n">
         <v>5</v>
@@ -19798,7 +19810,7 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O126" t="inlineStr">
@@ -19810,7 +19822,7 @@
         <v>3</v>
       </c>
       <c r="Q126" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R126" t="n">
         <v>1.5</v>
@@ -19825,7 +19837,7 @@
         <v>0.3</v>
       </c>
       <c r="V126" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W126" t="n">
         <v>5</v>
@@ -19952,7 +19964,7 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O127" t="inlineStr">
@@ -19964,7 +19976,7 @@
         <v>3</v>
       </c>
       <c r="Q127" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R127" t="n">
         <v>1.5</v>
@@ -19979,7 +19991,7 @@
         <v>0.3</v>
       </c>
       <c r="V127" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W127" t="n">
         <v>5</v>
@@ -20106,7 +20118,7 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O128" t="inlineStr">
@@ -20118,7 +20130,7 @@
         <v>3</v>
       </c>
       <c r="Q128" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R128" t="n">
         <v>1.5</v>
@@ -20133,7 +20145,7 @@
         <v>0.3</v>
       </c>
       <c r="V128" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W128" t="n">
         <v>5</v>
@@ -20260,7 +20272,7 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O129" t="inlineStr">
@@ -20272,7 +20284,7 @@
         <v>3</v>
       </c>
       <c r="Q129" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R129" t="n">
         <v>1.5</v>
@@ -20287,7 +20299,7 @@
         <v>0.3</v>
       </c>
       <c r="V129" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W129" t="n">
         <v>5</v>
@@ -20414,7 +20426,7 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O130" t="inlineStr">
@@ -20426,7 +20438,7 @@
         <v>3</v>
       </c>
       <c r="Q130" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R130" t="n">
         <v>1.5</v>
@@ -20441,7 +20453,7 @@
         <v>0.3</v>
       </c>
       <c r="V130" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W130" t="n">
         <v>5</v>
@@ -20568,7 +20580,7 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O131" t="inlineStr">
@@ -20580,7 +20592,7 @@
         <v>3</v>
       </c>
       <c r="Q131" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R131" t="n">
         <v>1.5</v>
@@ -20595,7 +20607,7 @@
         <v>0.3</v>
       </c>
       <c r="V131" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W131" t="n">
         <v>5</v>
@@ -20722,7 +20734,7 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O132" t="inlineStr">
@@ -20734,7 +20746,7 @@
         <v>3</v>
       </c>
       <c r="Q132" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R132" t="n">
         <v>1.5</v>
@@ -20749,7 +20761,7 @@
         <v>0.3</v>
       </c>
       <c r="V132" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W132" t="n">
         <v>5</v>
@@ -20876,7 +20888,7 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O133" t="inlineStr">
@@ -20888,7 +20900,7 @@
         <v>3</v>
       </c>
       <c r="Q133" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R133" t="n">
         <v>1.5</v>
@@ -20903,7 +20915,7 @@
         <v>0.3</v>
       </c>
       <c r="V133" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W133" t="n">
         <v>5</v>
@@ -21030,7 +21042,7 @@
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O134" t="inlineStr">
@@ -21042,7 +21054,7 @@
         <v>3</v>
       </c>
       <c r="Q134" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R134" t="n">
         <v>1.5</v>
@@ -21057,7 +21069,7 @@
         <v>0.3</v>
       </c>
       <c r="V134" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W134" t="n">
         <v>5</v>
@@ -21184,7 +21196,7 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O135" t="inlineStr">
@@ -21196,7 +21208,7 @@
         <v>3</v>
       </c>
       <c r="Q135" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R135" t="n">
         <v>1.5</v>
@@ -21211,7 +21223,7 @@
         <v>0.3</v>
       </c>
       <c r="V135" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W135" t="n">
         <v>5</v>
@@ -21338,7 +21350,7 @@
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O136" t="inlineStr">
@@ -21350,7 +21362,7 @@
         <v>3</v>
       </c>
       <c r="Q136" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R136" t="n">
         <v>1.5</v>
@@ -21365,7 +21377,7 @@
         <v>0.3</v>
       </c>
       <c r="V136" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W136" t="n">
         <v>5</v>
@@ -21492,7 +21504,7 @@
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O137" t="inlineStr">
@@ -21504,7 +21516,7 @@
         <v>3</v>
       </c>
       <c r="Q137" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R137" t="n">
         <v>1.5</v>
@@ -21519,7 +21531,7 @@
         <v>0.3</v>
       </c>
       <c r="V137" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W137" t="n">
         <v>5</v>
@@ -21646,7 +21658,7 @@
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O138" t="inlineStr">
@@ -21658,7 +21670,7 @@
         <v>3</v>
       </c>
       <c r="Q138" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R138" t="n">
         <v>1.5</v>
@@ -21673,7 +21685,7 @@
         <v>0.3</v>
       </c>
       <c r="V138" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W138" t="n">
         <v>5</v>
@@ -21800,7 +21812,7 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O139" t="inlineStr">
@@ -21812,7 +21824,7 @@
         <v>3</v>
       </c>
       <c r="Q139" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R139" t="n">
         <v>1.5</v>
@@ -21827,7 +21839,7 @@
         <v>0.3</v>
       </c>
       <c r="V139" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W139" t="n">
         <v>5</v>
@@ -21954,7 +21966,7 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O140" t="inlineStr">
@@ -21966,7 +21978,7 @@
         <v>3</v>
       </c>
       <c r="Q140" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R140" t="n">
         <v>1.5</v>
@@ -21981,7 +21993,7 @@
         <v>0.3</v>
       </c>
       <c r="V140" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W140" t="n">
         <v>5</v>
@@ -22108,7 +22120,7 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O141" t="inlineStr">
@@ -22120,7 +22132,7 @@
         <v>3</v>
       </c>
       <c r="Q141" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R141" t="n">
         <v>1.5</v>
@@ -22135,7 +22147,7 @@
         <v>0.3</v>
       </c>
       <c r="V141" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W141" t="n">
         <v>5</v>
@@ -22262,7 +22274,7 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O142" t="inlineStr">
@@ -22274,7 +22286,7 @@
         <v>3</v>
       </c>
       <c r="Q142" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R142" t="n">
         <v>1.5</v>
@@ -22289,7 +22301,7 @@
         <v>0.3</v>
       </c>
       <c r="V142" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W142" t="n">
         <v>5</v>
@@ -22416,7 +22428,7 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O143" t="inlineStr">
@@ -22428,7 +22440,7 @@
         <v>3</v>
       </c>
       <c r="Q143" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R143" t="n">
         <v>1.5</v>
@@ -22443,7 +22455,7 @@
         <v>0.3</v>
       </c>
       <c r="V143" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W143" t="n">
         <v>5</v>
@@ -22570,7 +22582,7 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O144" t="inlineStr">
@@ -22582,7 +22594,7 @@
         <v>3</v>
       </c>
       <c r="Q144" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R144" t="n">
         <v>1.5</v>
@@ -22597,7 +22609,7 @@
         <v>0.3</v>
       </c>
       <c r="V144" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W144" t="n">
         <v>5</v>
@@ -22724,7 +22736,7 @@
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O145" t="inlineStr">
@@ -22736,7 +22748,7 @@
         <v>3</v>
       </c>
       <c r="Q145" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R145" t="n">
         <v>1.5</v>
@@ -22751,7 +22763,7 @@
         <v>0.3</v>
       </c>
       <c r="V145" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W145" t="n">
         <v>5</v>
@@ -22878,7 +22890,7 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O146" t="inlineStr">
@@ -22890,7 +22902,7 @@
         <v>3</v>
       </c>
       <c r="Q146" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R146" t="n">
         <v>1.5</v>
@@ -22905,7 +22917,7 @@
         <v>0.3</v>
       </c>
       <c r="V146" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W146" t="n">
         <v>5</v>
@@ -23032,7 +23044,7 @@
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O147" t="inlineStr">
@@ -23044,7 +23056,7 @@
         <v>3</v>
       </c>
       <c r="Q147" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R147" t="n">
         <v>1.5</v>
@@ -23059,7 +23071,7 @@
         <v>0.3</v>
       </c>
       <c r="V147" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W147" t="n">
         <v>5</v>
@@ -23186,7 +23198,7 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O148" t="inlineStr">
@@ -23198,7 +23210,7 @@
         <v>3</v>
       </c>
       <c r="Q148" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R148" t="n">
         <v>1.5</v>
@@ -23213,7 +23225,7 @@
         <v>0.3</v>
       </c>
       <c r="V148" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W148" t="n">
         <v>5</v>
@@ -23340,7 +23352,7 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O149" t="inlineStr">
@@ -23352,7 +23364,7 @@
         <v>3</v>
       </c>
       <c r="Q149" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R149" t="n">
         <v>1.5</v>
@@ -23367,7 +23379,7 @@
         <v>0.3</v>
       </c>
       <c r="V149" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W149" t="n">
         <v>5</v>
@@ -23494,7 +23506,7 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O150" t="inlineStr">
@@ -23506,7 +23518,7 @@
         <v>3</v>
       </c>
       <c r="Q150" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R150" t="n">
         <v>1.5</v>
@@ -23521,7 +23533,7 @@
         <v>0.3</v>
       </c>
       <c r="V150" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W150" t="n">
         <v>5</v>
@@ -23648,7 +23660,7 @@
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O151" t="inlineStr">
@@ -23660,7 +23672,7 @@
         <v>3</v>
       </c>
       <c r="Q151" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R151" t="n">
         <v>1.5</v>
@@ -23675,7 +23687,7 @@
         <v>0.3</v>
       </c>
       <c r="V151" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W151" t="n">
         <v>5</v>
@@ -23802,7 +23814,7 @@
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O152" t="inlineStr">
@@ -23814,7 +23826,7 @@
         <v>3</v>
       </c>
       <c r="Q152" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R152" t="n">
         <v>1.5</v>
@@ -23829,7 +23841,7 @@
         <v>0.3</v>
       </c>
       <c r="V152" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W152" t="n">
         <v>5</v>
@@ -23956,7 +23968,7 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O153" t="inlineStr">
@@ -23968,7 +23980,7 @@
         <v>3</v>
       </c>
       <c r="Q153" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R153" t="n">
         <v>1.5</v>
@@ -23983,7 +23995,7 @@
         <v>0.3</v>
       </c>
       <c r="V153" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W153" t="n">
         <v>5</v>
@@ -24110,7 +24122,7 @@
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O154" t="inlineStr">
@@ -24122,7 +24134,7 @@
         <v>3</v>
       </c>
       <c r="Q154" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R154" t="n">
         <v>1.5</v>
@@ -24137,7 +24149,7 @@
         <v>0.3</v>
       </c>
       <c r="V154" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W154" t="n">
         <v>5</v>
@@ -24264,7 +24276,7 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O155" t="inlineStr">
@@ -24276,7 +24288,7 @@
         <v>3</v>
       </c>
       <c r="Q155" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R155" t="n">
         <v>1.5</v>
@@ -24291,7 +24303,7 @@
         <v>0.3</v>
       </c>
       <c r="V155" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W155" t="n">
         <v>5</v>
@@ -24418,7 +24430,7 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O156" t="inlineStr">
@@ -24430,7 +24442,7 @@
         <v>3</v>
       </c>
       <c r="Q156" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R156" t="n">
         <v>1.5</v>
@@ -24445,7 +24457,7 @@
         <v>0.3</v>
       </c>
       <c r="V156" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W156" t="n">
         <v>5</v>
@@ -24572,7 +24584,7 @@
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O157" t="inlineStr">
@@ -24584,7 +24596,7 @@
         <v>3</v>
       </c>
       <c r="Q157" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R157" t="n">
         <v>1.5</v>
@@ -24599,7 +24611,7 @@
         <v>0.3</v>
       </c>
       <c r="V157" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W157" t="n">
         <v>5</v>
@@ -24726,7 +24738,7 @@
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O158" t="inlineStr">
@@ -24738,7 +24750,7 @@
         <v>3</v>
       </c>
       <c r="Q158" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R158" t="n">
         <v>1.5</v>
@@ -24753,7 +24765,7 @@
         <v>0.3</v>
       </c>
       <c r="V158" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W158" t="n">
         <v>5</v>
@@ -24880,7 +24892,7 @@
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O159" t="inlineStr">
@@ -24892,7 +24904,7 @@
         <v>3</v>
       </c>
       <c r="Q159" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R159" t="n">
         <v>1.5</v>
@@ -24907,7 +24919,7 @@
         <v>0.3</v>
       </c>
       <c r="V159" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W159" t="n">
         <v>5</v>
@@ -25034,7 +25046,7 @@
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O160" t="inlineStr">
@@ -25046,7 +25058,7 @@
         <v>3</v>
       </c>
       <c r="Q160" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R160" t="n">
         <v>1.5</v>
@@ -25061,7 +25073,7 @@
         <v>0.3</v>
       </c>
       <c r="V160" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W160" t="n">
         <v>5</v>
@@ -25188,7 +25200,7 @@
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O161" t="inlineStr">
@@ -25200,7 +25212,7 @@
         <v>3</v>
       </c>
       <c r="Q161" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R161" t="n">
         <v>1.5</v>
@@ -25215,7 +25227,7 @@
         <v>0.3</v>
       </c>
       <c r="V161" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W161" t="n">
         <v>5</v>
@@ -25342,7 +25354,7 @@
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O162" t="inlineStr">
@@ -25354,7 +25366,7 @@
         <v>3</v>
       </c>
       <c r="Q162" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R162" t="n">
         <v>1.5</v>
@@ -25369,7 +25381,7 @@
         <v>0.3</v>
       </c>
       <c r="V162" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W162" t="n">
         <v>5</v>
@@ -25496,7 +25508,7 @@
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O163" t="inlineStr">
@@ -25508,7 +25520,7 @@
         <v>3</v>
       </c>
       <c r="Q163" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R163" t="n">
         <v>1.5</v>
@@ -25523,7 +25535,7 @@
         <v>0.3</v>
       </c>
       <c r="V163" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W163" t="n">
         <v>5</v>
@@ -25650,7 +25662,7 @@
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O164" t="inlineStr">
@@ -25662,7 +25674,7 @@
         <v>3</v>
       </c>
       <c r="Q164" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R164" t="n">
         <v>1.5</v>
@@ -25677,7 +25689,7 @@
         <v>0.3</v>
       </c>
       <c r="V164" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W164" t="n">
         <v>5</v>
@@ -25804,7 +25816,7 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O165" t="inlineStr">
@@ -25816,7 +25828,7 @@
         <v>3</v>
       </c>
       <c r="Q165" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R165" t="n">
         <v>1.5</v>
@@ -25831,7 +25843,7 @@
         <v>0.3</v>
       </c>
       <c r="V165" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W165" t="n">
         <v>5</v>
@@ -25958,7 +25970,7 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O166" t="inlineStr">
@@ -25970,7 +25982,7 @@
         <v>3</v>
       </c>
       <c r="Q166" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R166" t="n">
         <v>1.5</v>
@@ -25985,7 +25997,7 @@
         <v>0.3</v>
       </c>
       <c r="V166" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W166" t="n">
         <v>5</v>
@@ -26112,7 +26124,7 @@
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O167" t="inlineStr">
@@ -26124,7 +26136,7 @@
         <v>3</v>
       </c>
       <c r="Q167" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R167" t="n">
         <v>1.5</v>
@@ -26139,7 +26151,7 @@
         <v>0.3</v>
       </c>
       <c r="V167" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W167" t="n">
         <v>5</v>
@@ -26266,7 +26278,7 @@
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O168" t="inlineStr">
@@ -26278,7 +26290,7 @@
         <v>3</v>
       </c>
       <c r="Q168" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R168" t="n">
         <v>1.5</v>
@@ -26293,7 +26305,7 @@
         <v>0.3</v>
       </c>
       <c r="V168" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W168" t="n">
         <v>5</v>
@@ -26420,7 +26432,7 @@
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O169" t="inlineStr">
@@ -26432,7 +26444,7 @@
         <v>3</v>
       </c>
       <c r="Q169" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R169" t="n">
         <v>1.5</v>
@@ -26447,7 +26459,7 @@
         <v>0.3</v>
       </c>
       <c r="V169" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W169" t="n">
         <v>5</v>
@@ -26574,7 +26586,7 @@
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O170" t="inlineStr">
@@ -26586,7 +26598,7 @@
         <v>3</v>
       </c>
       <c r="Q170" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R170" t="n">
         <v>1.5</v>
@@ -26601,7 +26613,7 @@
         <v>0.3</v>
       </c>
       <c r="V170" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W170" t="n">
         <v>5</v>
@@ -26728,7 +26740,7 @@
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O171" t="inlineStr">
@@ -26740,7 +26752,7 @@
         <v>3</v>
       </c>
       <c r="Q171" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R171" t="n">
         <v>1.5</v>
@@ -26755,7 +26767,7 @@
         <v>0.3</v>
       </c>
       <c r="V171" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W171" t="n">
         <v>5</v>
@@ -26882,7 +26894,7 @@
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O172" t="inlineStr">
@@ -26894,7 +26906,7 @@
         <v>3</v>
       </c>
       <c r="Q172" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R172" t="n">
         <v>1.5</v>
@@ -26909,7 +26921,7 @@
         <v>0.3</v>
       </c>
       <c r="V172" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W172" t="n">
         <v>5</v>
@@ -27036,7 +27048,7 @@
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O173" t="inlineStr">
@@ -27048,7 +27060,7 @@
         <v>3</v>
       </c>
       <c r="Q173" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R173" t="n">
         <v>1.5</v>
@@ -27063,7 +27075,7 @@
         <v>0.3</v>
       </c>
       <c r="V173" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W173" t="n">
         <v>5</v>
@@ -27190,7 +27202,7 @@
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O174" t="inlineStr">
@@ -27202,7 +27214,7 @@
         <v>3</v>
       </c>
       <c r="Q174" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R174" t="n">
         <v>1.5</v>
@@ -27217,7 +27229,7 @@
         <v>0.3</v>
       </c>
       <c r="V174" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W174" t="n">
         <v>5</v>
@@ -27344,7 +27356,7 @@
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O175" t="inlineStr">
@@ -27356,7 +27368,7 @@
         <v>3</v>
       </c>
       <c r="Q175" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R175" t="n">
         <v>1.5</v>
@@ -27371,7 +27383,7 @@
         <v>0.3</v>
       </c>
       <c r="V175" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W175" t="n">
         <v>5</v>
@@ -27498,7 +27510,7 @@
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O176" t="inlineStr">
@@ -27510,7 +27522,7 @@
         <v>3</v>
       </c>
       <c r="Q176" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R176" t="n">
         <v>1.5</v>
@@ -27525,7 +27537,7 @@
         <v>0.3</v>
       </c>
       <c r="V176" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W176" t="n">
         <v>5</v>
@@ -27652,7 +27664,7 @@
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O177" t="inlineStr">
@@ -27664,7 +27676,7 @@
         <v>3</v>
       </c>
       <c r="Q177" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R177" t="n">
         <v>1.5</v>
@@ -27679,7 +27691,7 @@
         <v>0.3</v>
       </c>
       <c r="V177" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W177" t="n">
         <v>5</v>
@@ -27806,7 +27818,7 @@
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O178" t="inlineStr">
@@ -27818,7 +27830,7 @@
         <v>3</v>
       </c>
       <c r="Q178" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R178" t="n">
         <v>1.5</v>
@@ -27833,7 +27845,7 @@
         <v>0.3</v>
       </c>
       <c r="V178" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W178" t="n">
         <v>5</v>
@@ -27960,7 +27972,7 @@
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O179" t="inlineStr">
@@ -27972,7 +27984,7 @@
         <v>3</v>
       </c>
       <c r="Q179" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R179" t="n">
         <v>1.5</v>
@@ -27987,7 +27999,7 @@
         <v>0.3</v>
       </c>
       <c r="V179" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W179" t="n">
         <v>5</v>
@@ -28114,7 +28126,7 @@
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O180" t="inlineStr">
@@ -28126,7 +28138,7 @@
         <v>3</v>
       </c>
       <c r="Q180" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R180" t="n">
         <v>1.5</v>
@@ -28141,7 +28153,7 @@
         <v>0.3</v>
       </c>
       <c r="V180" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W180" t="n">
         <v>5</v>
@@ -28268,7 +28280,7 @@
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O181" t="inlineStr">
@@ -28280,7 +28292,7 @@
         <v>3</v>
       </c>
       <c r="Q181" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R181" t="n">
         <v>1.5</v>
@@ -28295,7 +28307,7 @@
         <v>0.3</v>
       </c>
       <c r="V181" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W181" t="n">
         <v>5</v>
@@ -28422,7 +28434,7 @@
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O182" t="inlineStr">
@@ -28434,7 +28446,7 @@
         <v>3</v>
       </c>
       <c r="Q182" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R182" t="n">
         <v>1.5</v>
@@ -28449,7 +28461,7 @@
         <v>0.3</v>
       </c>
       <c r="V182" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W182" t="n">
         <v>5</v>
@@ -28576,7 +28588,7 @@
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O183" t="inlineStr">
@@ -28588,7 +28600,7 @@
         <v>3</v>
       </c>
       <c r="Q183" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R183" t="n">
         <v>1.5</v>
@@ -28603,7 +28615,7 @@
         <v>0.3</v>
       </c>
       <c r="V183" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W183" t="n">
         <v>5</v>
@@ -28730,7 +28742,7 @@
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O184" t="inlineStr">
@@ -28742,7 +28754,7 @@
         <v>3</v>
       </c>
       <c r="Q184" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R184" t="n">
         <v>1.5</v>
@@ -28757,7 +28769,7 @@
         <v>0.3</v>
       </c>
       <c r="V184" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W184" t="n">
         <v>5</v>
@@ -28884,7 +28896,7 @@
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O185" t="inlineStr">
@@ -28896,7 +28908,7 @@
         <v>3</v>
       </c>
       <c r="Q185" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R185" t="n">
         <v>1.5</v>
@@ -28911,7 +28923,7 @@
         <v>0.3</v>
       </c>
       <c r="V185" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W185" t="n">
         <v>5</v>
@@ -29038,7 +29050,7 @@
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O186" t="inlineStr">
@@ -29050,7 +29062,7 @@
         <v>3</v>
       </c>
       <c r="Q186" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R186" t="n">
         <v>1.5</v>
@@ -29065,7 +29077,7 @@
         <v>0.3</v>
       </c>
       <c r="V186" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W186" t="n">
         <v>5</v>
@@ -29192,7 +29204,7 @@
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O187" t="inlineStr">
@@ -29204,7 +29216,7 @@
         <v>3</v>
       </c>
       <c r="Q187" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R187" t="n">
         <v>1.5</v>
@@ -29219,7 +29231,7 @@
         <v>0.3</v>
       </c>
       <c r="V187" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W187" t="n">
         <v>5</v>
@@ -29346,7 +29358,7 @@
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O188" t="inlineStr">
@@ -29358,7 +29370,7 @@
         <v>3</v>
       </c>
       <c r="Q188" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R188" t="n">
         <v>1.5</v>
@@ -29373,7 +29385,7 @@
         <v>0.3</v>
       </c>
       <c r="V188" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W188" t="n">
         <v>5</v>
@@ -29500,7 +29512,7 @@
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O189" t="inlineStr">
@@ -29512,7 +29524,7 @@
         <v>3</v>
       </c>
       <c r="Q189" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R189" t="n">
         <v>1.5</v>
@@ -29527,7 +29539,7 @@
         <v>0.3</v>
       </c>
       <c r="V189" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W189" t="n">
         <v>5</v>
@@ -29654,7 +29666,7 @@
       </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O190" t="inlineStr">
@@ -29666,7 +29678,7 @@
         <v>3</v>
       </c>
       <c r="Q190" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R190" t="n">
         <v>1.5</v>
@@ -29681,7 +29693,7 @@
         <v>0.3</v>
       </c>
       <c r="V190" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W190" t="n">
         <v>5</v>
@@ -29808,7 +29820,7 @@
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O191" t="inlineStr">
@@ -29820,7 +29832,7 @@
         <v>3</v>
       </c>
       <c r="Q191" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R191" t="n">
         <v>1.5</v>
@@ -29835,7 +29847,7 @@
         <v>0.3</v>
       </c>
       <c r="V191" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W191" t="n">
         <v>5</v>
@@ -29962,7 +29974,7 @@
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O192" t="inlineStr">
@@ -29974,7 +29986,7 @@
         <v>3</v>
       </c>
       <c r="Q192" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R192" t="n">
         <v>1.5</v>
@@ -29989,7 +30001,7 @@
         <v>0.3</v>
       </c>
       <c r="V192" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W192" t="n">
         <v>5</v>
@@ -30116,7 +30128,7 @@
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O193" t="inlineStr">
@@ -30128,7 +30140,7 @@
         <v>3</v>
       </c>
       <c r="Q193" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R193" t="n">
         <v>1.5</v>
@@ -30143,7 +30155,7 @@
         <v>0.3</v>
       </c>
       <c r="V193" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W193" t="n">
         <v>5</v>
@@ -30270,7 +30282,7 @@
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O194" t="inlineStr">
@@ -30282,7 +30294,7 @@
         <v>3</v>
       </c>
       <c r="Q194" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R194" t="n">
         <v>1.5</v>
@@ -30297,7 +30309,7 @@
         <v>0.3</v>
       </c>
       <c r="V194" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W194" t="n">
         <v>5</v>
@@ -30424,7 +30436,7 @@
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O195" t="inlineStr">
@@ -30436,7 +30448,7 @@
         <v>3</v>
       </c>
       <c r="Q195" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R195" t="n">
         <v>1.5</v>
@@ -30451,7 +30463,7 @@
         <v>0.3</v>
       </c>
       <c r="V195" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W195" t="n">
         <v>5</v>
@@ -30578,7 +30590,7 @@
       </c>
       <c r="N196" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O196" t="inlineStr">
@@ -30590,7 +30602,7 @@
         <v>3</v>
       </c>
       <c r="Q196" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R196" t="n">
         <v>1.5</v>
@@ -30605,7 +30617,7 @@
         <v>0.3</v>
       </c>
       <c r="V196" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W196" t="n">
         <v>5</v>
@@ -30732,7 +30744,7 @@
       </c>
       <c r="N197" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O197" t="inlineStr">
@@ -30744,7 +30756,7 @@
         <v>3</v>
       </c>
       <c r="Q197" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R197" t="n">
         <v>1.5</v>
@@ -30759,7 +30771,7 @@
         <v>0.3</v>
       </c>
       <c r="V197" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W197" t="n">
         <v>5</v>
@@ -30886,7 +30898,7 @@
       </c>
       <c r="N198" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O198" t="inlineStr">
@@ -30898,7 +30910,7 @@
         <v>3</v>
       </c>
       <c r="Q198" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R198" t="n">
         <v>1.5</v>
@@ -30913,7 +30925,7 @@
         <v>0.3</v>
       </c>
       <c r="V198" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W198" t="n">
         <v>5</v>
@@ -31040,7 +31052,7 @@
       </c>
       <c r="N199" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O199" t="inlineStr">
@@ -31052,7 +31064,7 @@
         <v>3</v>
       </c>
       <c r="Q199" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R199" t="n">
         <v>1.5</v>
@@ -31067,7 +31079,7 @@
         <v>0.3</v>
       </c>
       <c r="V199" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W199" t="n">
         <v>5</v>
@@ -31194,7 +31206,7 @@
       </c>
       <c r="N200" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O200" t="inlineStr">
@@ -31206,7 +31218,7 @@
         <v>3</v>
       </c>
       <c r="Q200" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R200" t="n">
         <v>1.5</v>
@@ -31221,7 +31233,7 @@
         <v>0.3</v>
       </c>
       <c r="V200" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W200" t="n">
         <v>5</v>
@@ -31348,7 +31360,7 @@
       </c>
       <c r="N201" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O201" t="inlineStr">
@@ -31360,7 +31372,7 @@
         <v>3</v>
       </c>
       <c r="Q201" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R201" t="n">
         <v>1.5</v>
@@ -31375,7 +31387,7 @@
         <v>0.3</v>
       </c>
       <c r="V201" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W201" t="n">
         <v>5</v>
@@ -31502,7 +31514,7 @@
       </c>
       <c r="N202" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O202" t="inlineStr">
@@ -31514,7 +31526,7 @@
         <v>3</v>
       </c>
       <c r="Q202" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R202" t="n">
         <v>1.5</v>
@@ -31529,7 +31541,7 @@
         <v>0.3</v>
       </c>
       <c r="V202" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W202" t="n">
         <v>5</v>
@@ -31656,7 +31668,7 @@
       </c>
       <c r="N203" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O203" t="inlineStr">
@@ -31668,7 +31680,7 @@
         <v>3</v>
       </c>
       <c r="Q203" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R203" t="n">
         <v>1.5</v>
@@ -31683,7 +31695,7 @@
         <v>0.3</v>
       </c>
       <c r="V203" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W203" t="n">
         <v>5</v>
@@ -31810,7 +31822,7 @@
       </c>
       <c r="N204" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O204" t="inlineStr">
@@ -31822,7 +31834,7 @@
         <v>3</v>
       </c>
       <c r="Q204" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R204" t="n">
         <v>1.5</v>
@@ -31837,7 +31849,7 @@
         <v>0.3</v>
       </c>
       <c r="V204" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W204" t="n">
         <v>5</v>
@@ -31964,7 +31976,7 @@
       </c>
       <c r="N205" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O205" t="inlineStr">
@@ -31976,7 +31988,7 @@
         <v>3</v>
       </c>
       <c r="Q205" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R205" t="n">
         <v>1.5</v>
@@ -31991,7 +32003,7 @@
         <v>0.3</v>
       </c>
       <c r="V205" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W205" t="n">
         <v>5</v>
@@ -32118,7 +32130,7 @@
       </c>
       <c r="N206" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O206" t="inlineStr">
@@ -32130,7 +32142,7 @@
         <v>3</v>
       </c>
       <c r="Q206" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R206" t="n">
         <v>1.5</v>
@@ -32145,7 +32157,7 @@
         <v>0.3</v>
       </c>
       <c r="V206" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W206" t="n">
         <v>5</v>
@@ -32272,7 +32284,7 @@
       </c>
       <c r="N207" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O207" t="inlineStr">
@@ -32284,7 +32296,7 @@
         <v>3</v>
       </c>
       <c r="Q207" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R207" t="n">
         <v>1.5</v>
@@ -32299,7 +32311,7 @@
         <v>0.3</v>
       </c>
       <c r="V207" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W207" t="n">
         <v>5</v>
@@ -32426,7 +32438,7 @@
       </c>
       <c r="N208" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O208" t="inlineStr">
@@ -32438,7 +32450,7 @@
         <v>3</v>
       </c>
       <c r="Q208" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R208" t="n">
         <v>1.5</v>
@@ -32453,7 +32465,7 @@
         <v>0.3</v>
       </c>
       <c r="V208" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W208" t="n">
         <v>5</v>
@@ -32580,7 +32592,7 @@
       </c>
       <c r="N209" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O209" t="inlineStr">
@@ -32592,7 +32604,7 @@
         <v>3</v>
       </c>
       <c r="Q209" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R209" t="n">
         <v>1.5</v>
@@ -32607,7 +32619,7 @@
         <v>0.3</v>
       </c>
       <c r="V209" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W209" t="n">
         <v>5</v>
@@ -32734,7 +32746,7 @@
       </c>
       <c r="N210" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O210" t="inlineStr">
@@ -32746,7 +32758,7 @@
         <v>3</v>
       </c>
       <c r="Q210" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R210" t="n">
         <v>1.5</v>
@@ -32761,7 +32773,7 @@
         <v>0.3</v>
       </c>
       <c r="V210" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W210" t="n">
         <v>5</v>
@@ -32888,7 +32900,7 @@
       </c>
       <c r="N211" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O211" t="inlineStr">
@@ -32900,7 +32912,7 @@
         <v>3</v>
       </c>
       <c r="Q211" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R211" t="n">
         <v>1.5</v>
@@ -32915,7 +32927,7 @@
         <v>0.3</v>
       </c>
       <c r="V211" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W211" t="n">
         <v>5</v>
@@ -33042,7 +33054,7 @@
       </c>
       <c r="N212" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O212" t="inlineStr">
@@ -33054,7 +33066,7 @@
         <v>3</v>
       </c>
       <c r="Q212" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R212" t="n">
         <v>1.5</v>
@@ -33069,7 +33081,7 @@
         <v>0.3</v>
       </c>
       <c r="V212" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W212" t="n">
         <v>5</v>
@@ -33196,7 +33208,7 @@
       </c>
       <c r="N213" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O213" t="inlineStr">
@@ -33208,7 +33220,7 @@
         <v>3</v>
       </c>
       <c r="Q213" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R213" t="n">
         <v>1.5</v>
@@ -33223,7 +33235,7 @@
         <v>0.3</v>
       </c>
       <c r="V213" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W213" t="n">
         <v>5</v>
@@ -33350,7 +33362,7 @@
       </c>
       <c r="N214" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O214" t="inlineStr">
@@ -33362,7 +33374,7 @@
         <v>3</v>
       </c>
       <c r="Q214" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R214" t="n">
         <v>1.5</v>
@@ -33377,7 +33389,7 @@
         <v>0.3</v>
       </c>
       <c r="V214" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W214" t="n">
         <v>5</v>
@@ -33504,7 +33516,7 @@
       </c>
       <c r="N215" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O215" t="inlineStr">
@@ -33516,7 +33528,7 @@
         <v>3</v>
       </c>
       <c r="Q215" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R215" t="n">
         <v>1.5</v>
@@ -33531,7 +33543,7 @@
         <v>0.3</v>
       </c>
       <c r="V215" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W215" t="n">
         <v>5</v>
@@ -33658,7 +33670,7 @@
       </c>
       <c r="N216" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O216" t="inlineStr">
@@ -33670,7 +33682,7 @@
         <v>3</v>
       </c>
       <c r="Q216" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R216" t="n">
         <v>1.5</v>
@@ -33685,7 +33697,7 @@
         <v>0.3</v>
       </c>
       <c r="V216" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W216" t="n">
         <v>5</v>
@@ -33812,7 +33824,7 @@
       </c>
       <c r="N217" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O217" t="inlineStr">
@@ -33824,7 +33836,7 @@
         <v>3</v>
       </c>
       <c r="Q217" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R217" t="n">
         <v>1.5</v>
@@ -33839,7 +33851,7 @@
         <v>0.3</v>
       </c>
       <c r="V217" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W217" t="n">
         <v>5</v>
@@ -33966,7 +33978,7 @@
       </c>
       <c r="N218" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O218" t="inlineStr">
@@ -33978,7 +33990,7 @@
         <v>3</v>
       </c>
       <c r="Q218" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R218" t="n">
         <v>1.5</v>
@@ -33993,7 +34005,7 @@
         <v>0.3</v>
       </c>
       <c r="V218" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W218" t="n">
         <v>5</v>
@@ -34120,7 +34132,7 @@
       </c>
       <c r="N219" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O219" t="inlineStr">
@@ -34132,7 +34144,7 @@
         <v>3</v>
       </c>
       <c r="Q219" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R219" t="n">
         <v>1.5</v>
@@ -34147,7 +34159,7 @@
         <v>0.3</v>
       </c>
       <c r="V219" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W219" t="n">
         <v>5</v>
@@ -34274,7 +34286,7 @@
       </c>
       <c r="N220" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O220" t="inlineStr">
@@ -34286,7 +34298,7 @@
         <v>3</v>
       </c>
       <c r="Q220" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R220" t="n">
         <v>1.5</v>
@@ -34301,7 +34313,7 @@
         <v>0.3</v>
       </c>
       <c r="V220" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W220" t="n">
         <v>5</v>
@@ -34428,7 +34440,7 @@
       </c>
       <c r="N221" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O221" t="inlineStr">
@@ -34440,7 +34452,7 @@
         <v>3</v>
       </c>
       <c r="Q221" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R221" t="n">
         <v>1.5</v>
@@ -34455,7 +34467,7 @@
         <v>0.3</v>
       </c>
       <c r="V221" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W221" t="n">
         <v>5</v>
@@ -34582,7 +34594,7 @@
       </c>
       <c r="N222" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O222" t="inlineStr">
@@ -34594,7 +34606,7 @@
         <v>3</v>
       </c>
       <c r="Q222" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R222" t="n">
         <v>1.5</v>
@@ -34609,7 +34621,7 @@
         <v>0.3</v>
       </c>
       <c r="V222" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W222" t="n">
         <v>5</v>
@@ -34736,7 +34748,7 @@
       </c>
       <c r="N223" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O223" t="inlineStr">
@@ -34748,7 +34760,7 @@
         <v>3</v>
       </c>
       <c r="Q223" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R223" t="n">
         <v>1.5</v>
@@ -34763,7 +34775,7 @@
         <v>0.3</v>
       </c>
       <c r="V223" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W223" t="n">
         <v>5</v>
@@ -34890,7 +34902,7 @@
       </c>
       <c r="N224" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O224" t="inlineStr">
@@ -34902,7 +34914,7 @@
         <v>3</v>
       </c>
       <c r="Q224" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R224" t="n">
         <v>1.5</v>
@@ -34917,7 +34929,7 @@
         <v>0.3</v>
       </c>
       <c r="V224" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W224" t="n">
         <v>5</v>
@@ -35044,7 +35056,7 @@
       </c>
       <c r="N225" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O225" t="inlineStr">
@@ -35056,7 +35068,7 @@
         <v>3</v>
       </c>
       <c r="Q225" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R225" t="n">
         <v>1.5</v>
@@ -35071,7 +35083,7 @@
         <v>0.3</v>
       </c>
       <c r="V225" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W225" t="n">
         <v>5</v>
@@ -35198,7 +35210,7 @@
       </c>
       <c r="N226" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O226" t="inlineStr">
@@ -35210,7 +35222,7 @@
         <v>3</v>
       </c>
       <c r="Q226" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R226" t="n">
         <v>1.5</v>
@@ -35225,7 +35237,7 @@
         <v>0.3</v>
       </c>
       <c r="V226" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W226" t="n">
         <v>5</v>
@@ -35352,7 +35364,7 @@
       </c>
       <c r="N227" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O227" t="inlineStr">
@@ -35364,7 +35376,7 @@
         <v>3</v>
       </c>
       <c r="Q227" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R227" t="n">
         <v>1.5</v>
@@ -35379,7 +35391,7 @@
         <v>0.3</v>
       </c>
       <c r="V227" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W227" t="n">
         <v>5</v>
@@ -35506,7 +35518,7 @@
       </c>
       <c r="N228" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O228" t="inlineStr">
@@ -35518,7 +35530,7 @@
         <v>3</v>
       </c>
       <c r="Q228" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R228" t="n">
         <v>1.5</v>
@@ -35533,7 +35545,7 @@
         <v>0.3</v>
       </c>
       <c r="V228" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W228" t="n">
         <v>5</v>
@@ -35660,7 +35672,7 @@
       </c>
       <c r="N229" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O229" t="inlineStr">
@@ -35672,7 +35684,7 @@
         <v>3</v>
       </c>
       <c r="Q229" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R229" t="n">
         <v>1.5</v>
@@ -35687,7 +35699,7 @@
         <v>0.3</v>
       </c>
       <c r="V229" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W229" t="n">
         <v>5</v>
@@ -35814,7 +35826,7 @@
       </c>
       <c r="N230" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O230" t="inlineStr">
@@ -35826,7 +35838,7 @@
         <v>3</v>
       </c>
       <c r="Q230" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R230" t="n">
         <v>1.5</v>
@@ -35841,7 +35853,7 @@
         <v>0.3</v>
       </c>
       <c r="V230" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W230" t="n">
         <v>5</v>
@@ -35968,7 +35980,7 @@
       </c>
       <c r="N231" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O231" t="inlineStr">
@@ -35980,7 +35992,7 @@
         <v>3</v>
       </c>
       <c r="Q231" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R231" t="n">
         <v>1.5</v>
@@ -35995,7 +36007,7 @@
         <v>0.3</v>
       </c>
       <c r="V231" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W231" t="n">
         <v>5</v>
@@ -36122,7 +36134,7 @@
       </c>
       <c r="N232" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O232" t="inlineStr">
@@ -36134,7 +36146,7 @@
         <v>3</v>
       </c>
       <c r="Q232" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R232" t="n">
         <v>1.5</v>
@@ -36149,7 +36161,7 @@
         <v>0.3</v>
       </c>
       <c r="V232" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W232" t="n">
         <v>5</v>
@@ -36276,7 +36288,7 @@
       </c>
       <c r="N233" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O233" t="inlineStr">
@@ -36288,7 +36300,7 @@
         <v>3</v>
       </c>
       <c r="Q233" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R233" t="n">
         <v>1.5</v>
@@ -36303,7 +36315,7 @@
         <v>0.3</v>
       </c>
       <c r="V233" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W233" t="n">
         <v>5</v>
@@ -36430,7 +36442,7 @@
       </c>
       <c r="N234" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O234" t="inlineStr">
@@ -36442,7 +36454,7 @@
         <v>3</v>
       </c>
       <c r="Q234" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R234" t="n">
         <v>1.5</v>
@@ -36457,7 +36469,7 @@
         <v>0.3</v>
       </c>
       <c r="V234" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W234" t="n">
         <v>5</v>
@@ -36584,7 +36596,7 @@
       </c>
       <c r="N235" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O235" t="inlineStr">
@@ -36596,7 +36608,7 @@
         <v>3</v>
       </c>
       <c r="Q235" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R235" t="n">
         <v>1.5</v>
@@ -36611,7 +36623,7 @@
         <v>0.3</v>
       </c>
       <c r="V235" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W235" t="n">
         <v>5</v>
@@ -36738,7 +36750,7 @@
       </c>
       <c r="N236" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O236" t="inlineStr">
@@ -36750,7 +36762,7 @@
         <v>3</v>
       </c>
       <c r="Q236" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R236" t="n">
         <v>1.5</v>
@@ -36765,7 +36777,7 @@
         <v>0.3</v>
       </c>
       <c r="V236" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W236" t="n">
         <v>5</v>
@@ -36892,7 +36904,7 @@
       </c>
       <c r="N237" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O237" t="inlineStr">
@@ -36904,7 +36916,7 @@
         <v>3</v>
       </c>
       <c r="Q237" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R237" t="n">
         <v>1.5</v>
@@ -36919,7 +36931,7 @@
         <v>0.3</v>
       </c>
       <c r="V237" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W237" t="n">
         <v>5</v>
@@ -37046,7 +37058,7 @@
       </c>
       <c r="N238" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O238" t="inlineStr">
@@ -37058,7 +37070,7 @@
         <v>3</v>
       </c>
       <c r="Q238" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R238" t="n">
         <v>1.5</v>
@@ -37073,7 +37085,7 @@
         <v>0.3</v>
       </c>
       <c r="V238" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W238" t="n">
         <v>5</v>
@@ -37200,7 +37212,7 @@
       </c>
       <c r="N239" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O239" t="inlineStr">
@@ -37212,7 +37224,7 @@
         <v>3</v>
       </c>
       <c r="Q239" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R239" t="n">
         <v>1.5</v>
@@ -37227,7 +37239,7 @@
         <v>0.3</v>
       </c>
       <c r="V239" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W239" t="n">
         <v>5</v>
@@ -37354,7 +37366,7 @@
       </c>
       <c r="N240" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O240" t="inlineStr">
@@ -37366,7 +37378,7 @@
         <v>3</v>
       </c>
       <c r="Q240" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R240" t="n">
         <v>1.5</v>
@@ -37381,7 +37393,7 @@
         <v>0.3</v>
       </c>
       <c r="V240" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W240" t="n">
         <v>5</v>
@@ -37508,7 +37520,7 @@
       </c>
       <c r="N241" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O241" t="inlineStr">
@@ -37520,7 +37532,7 @@
         <v>3</v>
       </c>
       <c r="Q241" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R241" t="n">
         <v>1.5</v>
@@ -37535,7 +37547,7 @@
         <v>0.3</v>
       </c>
       <c r="V241" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W241" t="n">
         <v>5</v>
@@ -37662,7 +37674,7 @@
       </c>
       <c r="N242" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O242" t="inlineStr">
@@ -37674,7 +37686,7 @@
         <v>3</v>
       </c>
       <c r="Q242" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R242" t="n">
         <v>1.5</v>
@@ -37689,7 +37701,7 @@
         <v>0.3</v>
       </c>
       <c r="V242" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W242" t="n">
         <v>5</v>
@@ -37816,7 +37828,7 @@
       </c>
       <c r="N243" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O243" t="inlineStr">
@@ -37828,7 +37840,7 @@
         <v>3</v>
       </c>
       <c r="Q243" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R243" t="n">
         <v>1.5</v>
@@ -37843,7 +37855,7 @@
         <v>0.3</v>
       </c>
       <c r="V243" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W243" t="n">
         <v>5</v>
@@ -37970,7 +37982,7 @@
       </c>
       <c r="N244" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O244" t="inlineStr">
@@ -37982,7 +37994,7 @@
         <v>3</v>
       </c>
       <c r="Q244" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R244" t="n">
         <v>1.5</v>
@@ -37997,7 +38009,7 @@
         <v>0.3</v>
       </c>
       <c r="V244" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W244" t="n">
         <v>5</v>
@@ -38124,7 +38136,7 @@
       </c>
       <c r="N245" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O245" t="inlineStr">
@@ -38136,7 +38148,7 @@
         <v>3</v>
       </c>
       <c r="Q245" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R245" t="n">
         <v>1.5</v>
@@ -38151,7 +38163,7 @@
         <v>0.3</v>
       </c>
       <c r="V245" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W245" t="n">
         <v>5</v>
@@ -38278,7 +38290,7 @@
       </c>
       <c r="N246" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O246" t="inlineStr">
@@ -38290,7 +38302,7 @@
         <v>3</v>
       </c>
       <c r="Q246" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R246" t="n">
         <v>1.5</v>
@@ -38305,7 +38317,7 @@
         <v>0.3</v>
       </c>
       <c r="V246" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W246" t="n">
         <v>5</v>
@@ -38432,7 +38444,7 @@
       </c>
       <c r="N247" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O247" t="inlineStr">
@@ -38444,7 +38456,7 @@
         <v>3</v>
       </c>
       <c r="Q247" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R247" t="n">
         <v>1.5</v>
@@ -38459,7 +38471,7 @@
         <v>0.3</v>
       </c>
       <c r="V247" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W247" t="n">
         <v>5</v>
@@ -38586,7 +38598,7 @@
       </c>
       <c r="N248" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O248" t="inlineStr">
@@ -38598,7 +38610,7 @@
         <v>3</v>
       </c>
       <c r="Q248" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R248" t="n">
         <v>1.5</v>
@@ -38613,7 +38625,7 @@
         <v>0.3</v>
       </c>
       <c r="V248" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W248" t="n">
         <v>5</v>
@@ -38740,7 +38752,7 @@
       </c>
       <c r="N249" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O249" t="inlineStr">
@@ -38752,7 +38764,7 @@
         <v>3</v>
       </c>
       <c r="Q249" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R249" t="n">
         <v>1.5</v>
@@ -38767,7 +38779,7 @@
         <v>0.3</v>
       </c>
       <c r="V249" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W249" t="n">
         <v>5</v>
@@ -38894,7 +38906,7 @@
       </c>
       <c r="N250" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O250" t="inlineStr">
@@ -38906,7 +38918,7 @@
         <v>3</v>
       </c>
       <c r="Q250" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R250" t="n">
         <v>1.5</v>
@@ -38921,7 +38933,7 @@
         <v>0.3</v>
       </c>
       <c r="V250" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W250" t="n">
         <v>5</v>
@@ -39048,7 +39060,7 @@
       </c>
       <c r="N251" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O251" t="inlineStr">
@@ -39060,7 +39072,7 @@
         <v>3</v>
       </c>
       <c r="Q251" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R251" t="n">
         <v>1.5</v>
@@ -39075,7 +39087,7 @@
         <v>0.3</v>
       </c>
       <c r="V251" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W251" t="n">
         <v>5</v>
@@ -39202,7 +39214,7 @@
       </c>
       <c r="N252" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O252" t="inlineStr">
@@ -39214,7 +39226,7 @@
         <v>3</v>
       </c>
       <c r="Q252" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R252" t="n">
         <v>1.5</v>
@@ -39229,7 +39241,7 @@
         <v>0.3</v>
       </c>
       <c r="V252" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W252" t="n">
         <v>5</v>
@@ -39356,7 +39368,7 @@
       </c>
       <c r="N253" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O253" t="inlineStr">
@@ -39368,7 +39380,7 @@
         <v>3</v>
       </c>
       <c r="Q253" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R253" t="n">
         <v>1.5</v>
@@ -39383,7 +39395,7 @@
         <v>0.3</v>
       </c>
       <c r="V253" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W253" t="n">
         <v>5</v>
@@ -39510,7 +39522,7 @@
       </c>
       <c r="N254" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O254" t="inlineStr">
@@ -39522,7 +39534,7 @@
         <v>3</v>
       </c>
       <c r="Q254" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R254" t="n">
         <v>1.5</v>
@@ -39537,7 +39549,7 @@
         <v>0.3</v>
       </c>
       <c r="V254" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W254" t="n">
         <v>5</v>
@@ -39664,7 +39676,7 @@
       </c>
       <c r="N255" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O255" t="inlineStr">
@@ -39676,7 +39688,7 @@
         <v>3</v>
       </c>
       <c r="Q255" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R255" t="n">
         <v>1.5</v>
@@ -39691,7 +39703,7 @@
         <v>0.3</v>
       </c>
       <c r="V255" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W255" t="n">
         <v>5</v>
@@ -39818,7 +39830,7 @@
       </c>
       <c r="N256" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O256" t="inlineStr">
@@ -39830,7 +39842,7 @@
         <v>3</v>
       </c>
       <c r="Q256" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R256" t="n">
         <v>1.5</v>
@@ -39845,7 +39857,7 @@
         <v>0.3</v>
       </c>
       <c r="V256" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W256" t="n">
         <v>5</v>
@@ -39972,7 +39984,7 @@
       </c>
       <c r="N257" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O257" t="inlineStr">
@@ -39984,7 +39996,7 @@
         <v>3</v>
       </c>
       <c r="Q257" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R257" t="n">
         <v>1.5</v>
@@ -39999,7 +40011,7 @@
         <v>0.3</v>
       </c>
       <c r="V257" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W257" t="n">
         <v>5</v>
@@ -40126,7 +40138,7 @@
       </c>
       <c r="N258" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O258" t="inlineStr">
@@ -40138,7 +40150,7 @@
         <v>3</v>
       </c>
       <c r="Q258" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R258" t="n">
         <v>1.5</v>
@@ -40153,7 +40165,7 @@
         <v>0.3</v>
       </c>
       <c r="V258" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W258" t="n">
         <v>5</v>
@@ -40280,7 +40292,7 @@
       </c>
       <c r="N259" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O259" t="inlineStr">
@@ -40292,7 +40304,7 @@
         <v>3</v>
       </c>
       <c r="Q259" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R259" t="n">
         <v>1.5</v>
@@ -40307,7 +40319,7 @@
         <v>0.3</v>
       </c>
       <c r="V259" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W259" t="n">
         <v>5</v>
@@ -40434,7 +40446,7 @@
       </c>
       <c r="N260" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O260" t="inlineStr">
@@ -40446,7 +40458,7 @@
         <v>3</v>
       </c>
       <c r="Q260" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R260" t="n">
         <v>1.5</v>
@@ -40461,7 +40473,7 @@
         <v>0.3</v>
       </c>
       <c r="V260" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W260" t="n">
         <v>5</v>
@@ -40588,7 +40600,7 @@
       </c>
       <c r="N261" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O261" t="inlineStr">
@@ -40600,7 +40612,7 @@
         <v>3</v>
       </c>
       <c r="Q261" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R261" t="n">
         <v>1.5</v>
@@ -40615,7 +40627,7 @@
         <v>0.3</v>
       </c>
       <c r="V261" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W261" t="n">
         <v>5</v>
@@ -40742,7 +40754,7 @@
       </c>
       <c r="N262" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O262" t="inlineStr">
@@ -40754,7 +40766,7 @@
         <v>3</v>
       </c>
       <c r="Q262" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R262" t="n">
         <v>1.5</v>
@@ -40769,7 +40781,7 @@
         <v>0.3</v>
       </c>
       <c r="V262" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W262" t="n">
         <v>5</v>
@@ -40896,7 +40908,7 @@
       </c>
       <c r="N263" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O263" t="inlineStr">
@@ -40908,7 +40920,7 @@
         <v>3</v>
       </c>
       <c r="Q263" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R263" t="n">
         <v>1.5</v>
@@ -40923,7 +40935,7 @@
         <v>0.3</v>
       </c>
       <c r="V263" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W263" t="n">
         <v>5</v>
@@ -41050,7 +41062,7 @@
       </c>
       <c r="N264" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O264" t="inlineStr">
@@ -41062,7 +41074,7 @@
         <v>3</v>
       </c>
       <c r="Q264" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R264" t="n">
         <v>1.5</v>
@@ -41077,7 +41089,7 @@
         <v>0.3</v>
       </c>
       <c r="V264" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W264" t="n">
         <v>5</v>
@@ -41204,7 +41216,7 @@
       </c>
       <c r="N265" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O265" t="inlineStr">
@@ -41216,7 +41228,7 @@
         <v>3</v>
       </c>
       <c r="Q265" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R265" t="n">
         <v>1.5</v>
@@ -41231,7 +41243,7 @@
         <v>0.3</v>
       </c>
       <c r="V265" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W265" t="n">
         <v>5</v>
@@ -41358,7 +41370,7 @@
       </c>
       <c r="N266" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O266" t="inlineStr">
@@ -41370,7 +41382,7 @@
         <v>3</v>
       </c>
       <c r="Q266" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R266" t="n">
         <v>1.5</v>
@@ -41385,7 +41397,7 @@
         <v>0.3</v>
       </c>
       <c r="V266" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W266" t="n">
         <v>5</v>
@@ -41512,7 +41524,7 @@
       </c>
       <c r="N267" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O267" t="inlineStr">
@@ -41524,7 +41536,7 @@
         <v>3</v>
       </c>
       <c r="Q267" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R267" t="n">
         <v>1.5</v>
@@ -41539,7 +41551,7 @@
         <v>0.3</v>
       </c>
       <c r="V267" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W267" t="n">
         <v>5</v>
@@ -41666,7 +41678,7 @@
       </c>
       <c r="N268" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O268" t="inlineStr">
@@ -41678,7 +41690,7 @@
         <v>3</v>
       </c>
       <c r="Q268" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R268" t="n">
         <v>1.5</v>
@@ -41693,7 +41705,7 @@
         <v>0.3</v>
       </c>
       <c r="V268" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W268" t="n">
         <v>5</v>
@@ -41820,7 +41832,7 @@
       </c>
       <c r="N269" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O269" t="inlineStr">
@@ -41832,7 +41844,7 @@
         <v>3</v>
       </c>
       <c r="Q269" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R269" t="n">
         <v>1.5</v>
@@ -41847,7 +41859,7 @@
         <v>0.3</v>
       </c>
       <c r="V269" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W269" t="n">
         <v>5</v>
@@ -41974,7 +41986,7 @@
       </c>
       <c r="N270" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O270" t="inlineStr">
@@ -41986,7 +41998,7 @@
         <v>3</v>
       </c>
       <c r="Q270" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R270" t="n">
         <v>1.5</v>
@@ -42001,7 +42013,7 @@
         <v>0.3</v>
       </c>
       <c r="V270" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W270" t="n">
         <v>5</v>
@@ -42128,7 +42140,7 @@
       </c>
       <c r="N271" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O271" t="inlineStr">
@@ -42140,7 +42152,7 @@
         <v>3</v>
       </c>
       <c r="Q271" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R271" t="n">
         <v>1.5</v>
@@ -42155,7 +42167,7 @@
         <v>0.3</v>
       </c>
       <c r="V271" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W271" t="n">
         <v>5</v>
@@ -42282,7 +42294,7 @@
       </c>
       <c r="N272" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O272" t="inlineStr">
@@ -42294,7 +42306,7 @@
         <v>3</v>
       </c>
       <c r="Q272" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R272" t="n">
         <v>1.5</v>
@@ -42309,7 +42321,7 @@
         <v>0.3</v>
       </c>
       <c r="V272" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W272" t="n">
         <v>5</v>
@@ -42436,7 +42448,7 @@
       </c>
       <c r="N273" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O273" t="inlineStr">
@@ -42448,7 +42460,7 @@
         <v>3</v>
       </c>
       <c r="Q273" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R273" t="n">
         <v>1.5</v>
@@ -42463,7 +42475,7 @@
         <v>0.3</v>
       </c>
       <c r="V273" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W273" t="n">
         <v>5</v>
@@ -42590,7 +42602,7 @@
       </c>
       <c r="N274" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O274" t="inlineStr">
@@ -42602,7 +42614,7 @@
         <v>3</v>
       </c>
       <c r="Q274" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R274" t="n">
         <v>1.5</v>
@@ -42617,7 +42629,7 @@
         <v>0.3</v>
       </c>
       <c r="V274" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W274" t="n">
         <v>5</v>
@@ -42744,7 +42756,7 @@
       </c>
       <c r="N275" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O275" t="inlineStr">
@@ -42756,7 +42768,7 @@
         <v>3</v>
       </c>
       <c r="Q275" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R275" t="n">
         <v>1.5</v>
@@ -42771,7 +42783,7 @@
         <v>0.3</v>
       </c>
       <c r="V275" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W275" t="n">
         <v>5</v>
@@ -42898,7 +42910,7 @@
       </c>
       <c r="N276" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O276" t="inlineStr">
@@ -42910,7 +42922,7 @@
         <v>3</v>
       </c>
       <c r="Q276" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R276" t="n">
         <v>1.5</v>
@@ -42925,7 +42937,7 @@
         <v>0.3</v>
       </c>
       <c r="V276" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W276" t="n">
         <v>5</v>
@@ -43052,7 +43064,7 @@
       </c>
       <c r="N277" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O277" t="inlineStr">
@@ -43064,7 +43076,7 @@
         <v>3</v>
       </c>
       <c r="Q277" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R277" t="n">
         <v>1.5</v>
@@ -43079,7 +43091,7 @@
         <v>0.3</v>
       </c>
       <c r="V277" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W277" t="n">
         <v>5</v>
@@ -43206,7 +43218,7 @@
       </c>
       <c r="N278" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O278" t="inlineStr">
@@ -43218,7 +43230,7 @@
         <v>3</v>
       </c>
       <c r="Q278" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R278" t="n">
         <v>1.5</v>
@@ -43233,7 +43245,7 @@
         <v>0.3</v>
       </c>
       <c r="V278" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W278" t="n">
         <v>5</v>
@@ -43360,7 +43372,7 @@
       </c>
       <c r="N279" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O279" t="inlineStr">
@@ -43372,7 +43384,7 @@
         <v>3</v>
       </c>
       <c r="Q279" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R279" t="n">
         <v>1.5</v>
@@ -43387,7 +43399,7 @@
         <v>0.3</v>
       </c>
       <c r="V279" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W279" t="n">
         <v>5</v>
@@ -43514,7 +43526,7 @@
       </c>
       <c r="N280" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O280" t="inlineStr">
@@ -43526,7 +43538,7 @@
         <v>3</v>
       </c>
       <c r="Q280" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R280" t="n">
         <v>1.5</v>
@@ -43541,7 +43553,7 @@
         <v>0.3</v>
       </c>
       <c r="V280" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W280" t="n">
         <v>5</v>
@@ -43668,7 +43680,7 @@
       </c>
       <c r="N281" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O281" t="inlineStr">
@@ -43680,7 +43692,7 @@
         <v>3</v>
       </c>
       <c r="Q281" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R281" t="n">
         <v>1.5</v>
@@ -43695,7 +43707,7 @@
         <v>0.3</v>
       </c>
       <c r="V281" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W281" t="n">
         <v>5</v>
@@ -43822,7 +43834,7 @@
       </c>
       <c r="N282" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O282" t="inlineStr">
@@ -43834,7 +43846,7 @@
         <v>3</v>
       </c>
       <c r="Q282" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R282" t="n">
         <v>1.5</v>
@@ -43849,7 +43861,7 @@
         <v>0.3</v>
       </c>
       <c r="V282" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W282" t="n">
         <v>5</v>
@@ -43976,7 +43988,7 @@
       </c>
       <c r="N283" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O283" t="inlineStr">
@@ -43988,7 +44000,7 @@
         <v>3</v>
       </c>
       <c r="Q283" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R283" t="n">
         <v>1.5</v>
@@ -44003,7 +44015,7 @@
         <v>0.3</v>
       </c>
       <c r="V283" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W283" t="n">
         <v>5</v>
@@ -44130,7 +44142,7 @@
       </c>
       <c r="N284" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O284" t="inlineStr">
@@ -44142,7 +44154,7 @@
         <v>3</v>
       </c>
       <c r="Q284" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R284" t="n">
         <v>1.5</v>
@@ -44157,7 +44169,7 @@
         <v>0.3</v>
       </c>
       <c r="V284" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W284" t="n">
         <v>5</v>
@@ -44284,7 +44296,7 @@
       </c>
       <c r="N285" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O285" t="inlineStr">
@@ -44296,7 +44308,7 @@
         <v>3</v>
       </c>
       <c r="Q285" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R285" t="n">
         <v>1.5</v>
@@ -44311,7 +44323,7 @@
         <v>0.3</v>
       </c>
       <c r="V285" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W285" t="n">
         <v>5</v>
@@ -44438,7 +44450,7 @@
       </c>
       <c r="N286" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O286" t="inlineStr">
@@ -44450,7 +44462,7 @@
         <v>3</v>
       </c>
       <c r="Q286" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R286" t="n">
         <v>1.5</v>
@@ -44465,7 +44477,7 @@
         <v>0.3</v>
       </c>
       <c r="V286" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W286" t="n">
         <v>5</v>
@@ -44592,7 +44604,7 @@
       </c>
       <c r="N287" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O287" t="inlineStr">
@@ -44604,7 +44616,7 @@
         <v>3</v>
       </c>
       <c r="Q287" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R287" t="n">
         <v>1.5</v>
@@ -44619,7 +44631,7 @@
         <v>0.3</v>
       </c>
       <c r="V287" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W287" t="n">
         <v>5</v>
@@ -44746,7 +44758,7 @@
       </c>
       <c r="N288" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O288" t="inlineStr">
@@ -44758,7 +44770,7 @@
         <v>3</v>
       </c>
       <c r="Q288" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R288" t="n">
         <v>1.5</v>
@@ -44773,7 +44785,7 @@
         <v>0.3</v>
       </c>
       <c r="V288" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W288" t="n">
         <v>5</v>
@@ -44900,7 +44912,7 @@
       </c>
       <c r="N289" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O289" t="inlineStr">
@@ -44912,7 +44924,7 @@
         <v>3</v>
       </c>
       <c r="Q289" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R289" t="n">
         <v>1.5</v>
@@ -44927,7 +44939,7 @@
         <v>0.3</v>
       </c>
       <c r="V289" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W289" t="n">
         <v>5</v>
@@ -45054,7 +45066,7 @@
       </c>
       <c r="N290" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O290" t="inlineStr">
@@ -45066,7 +45078,7 @@
         <v>3</v>
       </c>
       <c r="Q290" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R290" t="n">
         <v>1.5</v>
@@ -45081,7 +45093,7 @@
         <v>0.3</v>
       </c>
       <c r="V290" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W290" t="n">
         <v>5</v>
@@ -45208,7 +45220,7 @@
       </c>
       <c r="N291" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O291" t="inlineStr">
@@ -45220,7 +45232,7 @@
         <v>3</v>
       </c>
       <c r="Q291" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R291" t="n">
         <v>1.5</v>
@@ -45235,7 +45247,7 @@
         <v>0.3</v>
       </c>
       <c r="V291" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W291" t="n">
         <v>5</v>
@@ -45362,7 +45374,7 @@
       </c>
       <c r="N292" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O292" t="inlineStr">
@@ -45374,7 +45386,7 @@
         <v>3</v>
       </c>
       <c r="Q292" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R292" t="n">
         <v>1.5</v>
@@ -45389,7 +45401,7 @@
         <v>0.3</v>
       </c>
       <c r="V292" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W292" t="n">
         <v>5</v>
@@ -45516,7 +45528,7 @@
       </c>
       <c r="N293" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O293" t="inlineStr">
@@ -45528,7 +45540,7 @@
         <v>3</v>
       </c>
       <c r="Q293" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R293" t="n">
         <v>1.5</v>
@@ -45543,7 +45555,7 @@
         <v>0.3</v>
       </c>
       <c r="V293" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W293" t="n">
         <v>5</v>
@@ -45670,7 +45682,7 @@
       </c>
       <c r="N294" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O294" t="inlineStr">
@@ -45682,7 +45694,7 @@
         <v>3</v>
       </c>
       <c r="Q294" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R294" t="n">
         <v>1.5</v>
@@ -45697,7 +45709,7 @@
         <v>0.3</v>
       </c>
       <c r="V294" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W294" t="n">
         <v>5</v>
@@ -45824,7 +45836,7 @@
       </c>
       <c r="N295" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O295" t="inlineStr">
@@ -45836,7 +45848,7 @@
         <v>3</v>
       </c>
       <c r="Q295" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R295" t="n">
         <v>1.5</v>
@@ -45851,7 +45863,7 @@
         <v>0.3</v>
       </c>
       <c r="V295" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W295" t="n">
         <v>5</v>
@@ -45978,7 +45990,7 @@
       </c>
       <c r="N296" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O296" t="inlineStr">
@@ -45990,7 +46002,7 @@
         <v>3</v>
       </c>
       <c r="Q296" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R296" t="n">
         <v>1.5</v>
@@ -46005,7 +46017,7 @@
         <v>0.3</v>
       </c>
       <c r="V296" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W296" t="n">
         <v>5</v>
@@ -46132,7 +46144,7 @@
       </c>
       <c r="N297" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O297" t="inlineStr">
@@ -46144,7 +46156,7 @@
         <v>3</v>
       </c>
       <c r="Q297" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R297" t="n">
         <v>1.5</v>
@@ -46159,7 +46171,7 @@
         <v>0.3</v>
       </c>
       <c r="V297" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W297" t="n">
         <v>5</v>
@@ -46286,7 +46298,7 @@
       </c>
       <c r="N298" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O298" t="inlineStr">
@@ -46298,7 +46310,7 @@
         <v>3</v>
       </c>
       <c r="Q298" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R298" t="n">
         <v>1.5</v>
@@ -46313,7 +46325,7 @@
         <v>0.3</v>
       </c>
       <c r="V298" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W298" t="n">
         <v>5</v>
@@ -46440,7 +46452,7 @@
       </c>
       <c r="N299" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O299" t="inlineStr">
@@ -46452,7 +46464,7 @@
         <v>3</v>
       </c>
       <c r="Q299" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R299" t="n">
         <v>1.5</v>
@@ -46467,7 +46479,7 @@
         <v>0.3</v>
       </c>
       <c r="V299" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W299" t="n">
         <v>5</v>
@@ -46594,7 +46606,7 @@
       </c>
       <c r="N300" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O300" t="inlineStr">
@@ -46606,7 +46618,7 @@
         <v>3</v>
       </c>
       <c r="Q300" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R300" t="n">
         <v>1.5</v>
@@ -46621,7 +46633,7 @@
         <v>0.3</v>
       </c>
       <c r="V300" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W300" t="n">
         <v>5</v>
@@ -46748,7 +46760,7 @@
       </c>
       <c r="N301" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O301" t="inlineStr">
@@ -46760,7 +46772,7 @@
         <v>3</v>
       </c>
       <c r="Q301" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R301" t="n">
         <v>1.5</v>
@@ -46775,7 +46787,7 @@
         <v>0.3</v>
       </c>
       <c r="V301" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W301" t="n">
         <v>5</v>
@@ -46902,7 +46914,7 @@
       </c>
       <c r="N302" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O302" t="inlineStr">
@@ -46914,7 +46926,7 @@
         <v>3</v>
       </c>
       <c r="Q302" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R302" t="n">
         <v>1.5</v>
@@ -46929,7 +46941,7 @@
         <v>0.3</v>
       </c>
       <c r="V302" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W302" t="n">
         <v>5</v>
@@ -47056,7 +47068,7 @@
       </c>
       <c r="N303" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O303" t="inlineStr">
@@ -47068,7 +47080,7 @@
         <v>3</v>
       </c>
       <c r="Q303" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R303" t="n">
         <v>1.5</v>
@@ -47083,7 +47095,7 @@
         <v>0.3</v>
       </c>
       <c r="V303" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W303" t="n">
         <v>5</v>
@@ -47210,7 +47222,7 @@
       </c>
       <c r="N304" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O304" t="inlineStr">
@@ -47222,7 +47234,7 @@
         <v>3</v>
       </c>
       <c r="Q304" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R304" t="n">
         <v>1.5</v>
@@ -47237,7 +47249,7 @@
         <v>0.3</v>
       </c>
       <c r="V304" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W304" t="n">
         <v>5</v>
@@ -47364,7 +47376,7 @@
       </c>
       <c r="N305" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O305" t="inlineStr">
@@ -47376,7 +47388,7 @@
         <v>3</v>
       </c>
       <c r="Q305" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R305" t="n">
         <v>1.5</v>
@@ -47391,7 +47403,7 @@
         <v>0.3</v>
       </c>
       <c r="V305" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W305" t="n">
         <v>5</v>
@@ -47518,7 +47530,7 @@
       </c>
       <c r="N306" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O306" t="inlineStr">
@@ -47530,7 +47542,7 @@
         <v>3</v>
       </c>
       <c r="Q306" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R306" t="n">
         <v>1.5</v>
@@ -47545,7 +47557,7 @@
         <v>0.3</v>
       </c>
       <c r="V306" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W306" t="n">
         <v>5</v>
@@ -47672,7 +47684,7 @@
       </c>
       <c r="N307" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O307" t="inlineStr">
@@ -47684,7 +47696,7 @@
         <v>3</v>
       </c>
       <c r="Q307" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R307" t="n">
         <v>1.5</v>
@@ -47699,7 +47711,7 @@
         <v>0.3</v>
       </c>
       <c r="V307" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W307" t="n">
         <v>5</v>
@@ -47826,7 +47838,7 @@
       </c>
       <c r="N308" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O308" t="inlineStr">
@@ -47838,7 +47850,7 @@
         <v>3</v>
       </c>
       <c r="Q308" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R308" t="n">
         <v>1.5</v>
@@ -47853,7 +47865,7 @@
         <v>0.3</v>
       </c>
       <c r="V308" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W308" t="n">
         <v>5</v>
@@ -47980,7 +47992,7 @@
       </c>
       <c r="N309" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O309" t="inlineStr">
@@ -47992,7 +48004,7 @@
         <v>3</v>
       </c>
       <c r="Q309" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R309" t="n">
         <v>1.5</v>
@@ -48007,7 +48019,7 @@
         <v>0.3</v>
       </c>
       <c r="V309" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W309" t="n">
         <v>5</v>
@@ -48134,7 +48146,7 @@
       </c>
       <c r="N310" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O310" t="inlineStr">
@@ -48146,7 +48158,7 @@
         <v>3</v>
       </c>
       <c r="Q310" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R310" t="n">
         <v>1.5</v>
@@ -48161,7 +48173,7 @@
         <v>0.3</v>
       </c>
       <c r="V310" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W310" t="n">
         <v>5</v>
@@ -48288,7 +48300,7 @@
       </c>
       <c r="N311" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O311" t="inlineStr">
@@ -48300,7 +48312,7 @@
         <v>3</v>
       </c>
       <c r="Q311" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R311" t="n">
         <v>1.5</v>
@@ -48315,7 +48327,7 @@
         <v>0.3</v>
       </c>
       <c r="V311" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W311" t="n">
         <v>5</v>
@@ -48442,7 +48454,7 @@
       </c>
       <c r="N312" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O312" t="inlineStr">
@@ -48454,7 +48466,7 @@
         <v>3</v>
       </c>
       <c r="Q312" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R312" t="n">
         <v>1.5</v>
@@ -48469,7 +48481,7 @@
         <v>0.3</v>
       </c>
       <c r="V312" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W312" t="n">
         <v>5</v>
@@ -48596,7 +48608,7 @@
       </c>
       <c r="N313" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O313" t="inlineStr">
@@ -48608,7 +48620,7 @@
         <v>3</v>
       </c>
       <c r="Q313" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R313" t="n">
         <v>1.5</v>
@@ -48623,7 +48635,7 @@
         <v>0.3</v>
       </c>
       <c r="V313" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W313" t="n">
         <v>5</v>
@@ -48750,7 +48762,7 @@
       </c>
       <c r="N314" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O314" t="inlineStr">
@@ -48762,7 +48774,7 @@
         <v>3</v>
       </c>
       <c r="Q314" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R314" t="n">
         <v>1.5</v>
@@ -48777,7 +48789,7 @@
         <v>0.3</v>
       </c>
       <c r="V314" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W314" t="n">
         <v>5</v>
@@ -48904,7 +48916,7 @@
       </c>
       <c r="N315" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O315" t="inlineStr">
@@ -48916,7 +48928,7 @@
         <v>3</v>
       </c>
       <c r="Q315" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R315" t="n">
         <v>1.5</v>
@@ -48931,7 +48943,7 @@
         <v>0.3</v>
       </c>
       <c r="V315" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W315" t="n">
         <v>5</v>
@@ -49058,7 +49070,7 @@
       </c>
       <c r="N316" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O316" t="inlineStr">
@@ -49070,7 +49082,7 @@
         <v>3</v>
       </c>
       <c r="Q316" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R316" t="n">
         <v>1.5</v>
@@ -49085,7 +49097,7 @@
         <v>0.3</v>
       </c>
       <c r="V316" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W316" t="n">
         <v>5</v>
@@ -49212,7 +49224,7 @@
       </c>
       <c r="N317" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O317" t="inlineStr">
@@ -49224,7 +49236,7 @@
         <v>3</v>
       </c>
       <c r="Q317" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R317" t="n">
         <v>1.5</v>
@@ -49239,7 +49251,7 @@
         <v>0.3</v>
       </c>
       <c r="V317" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W317" t="n">
         <v>5</v>
@@ -49366,7 +49378,7 @@
       </c>
       <c r="N318" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O318" t="inlineStr">
@@ -49378,7 +49390,7 @@
         <v>3</v>
       </c>
       <c r="Q318" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R318" t="n">
         <v>1.5</v>
@@ -49393,7 +49405,7 @@
         <v>0.3</v>
       </c>
       <c r="V318" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W318" t="n">
         <v>5</v>
@@ -49520,7 +49532,7 @@
       </c>
       <c r="N319" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O319" t="inlineStr">
@@ -49532,7 +49544,7 @@
         <v>3</v>
       </c>
       <c r="Q319" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R319" t="n">
         <v>1.5</v>
@@ -49547,7 +49559,7 @@
         <v>0.3</v>
       </c>
       <c r="V319" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W319" t="n">
         <v>5</v>
@@ -49674,7 +49686,7 @@
       </c>
       <c r="N320" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O320" t="inlineStr">
@@ -49686,7 +49698,7 @@
         <v>3</v>
       </c>
       <c r="Q320" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R320" t="n">
         <v>1.5</v>
@@ -49701,7 +49713,7 @@
         <v>0.3</v>
       </c>
       <c r="V320" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W320" t="n">
         <v>5</v>
@@ -49828,7 +49840,7 @@
       </c>
       <c r="N321" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="O321" t="inlineStr">
@@ -49840,7 +49852,7 @@
         <v>3</v>
       </c>
       <c r="Q321" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R321" t="n">
         <v>1.5</v>
@@ -49855,7 +49867,7 @@
         <v>0.3</v>
       </c>
       <c r="V321" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W321" t="n">
         <v>5</v>

--- a/engstruct_casos.xlsx
+++ b/engstruct_casos.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>Módulo de elasticidade médio à flexão (GPa) da longarina (GPa)</t>
+          <t>Módulo de elasticidade à flexão (GPa) da longarina (GPa)</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
@@ -904,7 +904,7 @@
         <v>750</v>
       </c>
       <c r="Y3" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="Z3" t="n">
         <v>6</v>
@@ -916,7 +916,7 @@
         <v>750</v>
       </c>
       <c r="AC3" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="AD3" t="n">
         <v>30</v>
@@ -1212,7 +1212,7 @@
         <v>750</v>
       </c>
       <c r="Y5" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="Z5" t="n">
         <v>6</v>
@@ -1224,7 +1224,7 @@
         <v>750</v>
       </c>
       <c r="AC5" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="AD5" t="n">
         <v>30</v>
@@ -1520,7 +1520,7 @@
         <v>750</v>
       </c>
       <c r="Y7" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="Z7" t="n">
         <v>6</v>
@@ -1532,7 +1532,7 @@
         <v>750</v>
       </c>
       <c r="AC7" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="AD7" t="n">
         <v>30</v>
@@ -1828,7 +1828,7 @@
         <v>750</v>
       </c>
       <c r="Y9" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="Z9" t="n">
         <v>6</v>
@@ -1840,7 +1840,7 @@
         <v>750</v>
       </c>
       <c r="AC9" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="AD9" t="n">
         <v>30</v>
@@ -2136,7 +2136,7 @@
         <v>625</v>
       </c>
       <c r="Y11" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="Z11" t="n">
         <v>5</v>
@@ -2148,7 +2148,7 @@
         <v>625</v>
       </c>
       <c r="AC11" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="AD11" t="n">
         <v>30</v>
@@ -2444,7 +2444,7 @@
         <v>625</v>
       </c>
       <c r="Y13" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="Z13" t="n">
         <v>5</v>
@@ -2456,7 +2456,7 @@
         <v>625</v>
       </c>
       <c r="AC13" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="AD13" t="n">
         <v>30</v>
@@ -2752,7 +2752,7 @@
         <v>625</v>
       </c>
       <c r="Y15" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="Z15" t="n">
         <v>5</v>
@@ -2764,7 +2764,7 @@
         <v>625</v>
       </c>
       <c r="AC15" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="AD15" t="n">
         <v>30</v>
@@ -3060,7 +3060,7 @@
         <v>625</v>
       </c>
       <c r="Y17" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="Z17" t="n">
         <v>5</v>
@@ -3072,7 +3072,7 @@
         <v>625</v>
       </c>
       <c r="AC17" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="AD17" t="n">
         <v>30</v>
@@ -3368,7 +3368,7 @@
         <v>850</v>
       </c>
       <c r="Y19" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="Z19" t="n">
         <v>7</v>
@@ -3380,7 +3380,7 @@
         <v>850</v>
       </c>
       <c r="AC19" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="AD19" t="n">
         <v>30</v>
@@ -3676,7 +3676,7 @@
         <v>850</v>
       </c>
       <c r="Y21" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="Z21" t="n">
         <v>7</v>
@@ -3688,7 +3688,7 @@
         <v>850</v>
       </c>
       <c r="AC21" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="AD21" t="n">
         <v>30</v>
@@ -3984,7 +3984,7 @@
         <v>850</v>
       </c>
       <c r="Y23" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="Z23" t="n">
         <v>7</v>
@@ -3996,7 +3996,7 @@
         <v>850</v>
       </c>
       <c r="AC23" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="AD23" t="n">
         <v>30</v>
@@ -4292,7 +4292,7 @@
         <v>850</v>
       </c>
       <c r="Y25" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="Z25" t="n">
         <v>7</v>
@@ -4304,7 +4304,7 @@
         <v>850</v>
       </c>
       <c r="AC25" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="AD25" t="n">
         <v>30</v>
@@ -4600,7 +4600,7 @@
         <v>850</v>
       </c>
       <c r="Y27" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="Z27" t="n">
         <v>7</v>
@@ -4612,7 +4612,7 @@
         <v>850</v>
       </c>
       <c r="AC27" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="AD27" t="n">
         <v>30</v>
@@ -4908,7 +4908,7 @@
         <v>850</v>
       </c>
       <c r="Y29" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="Z29" t="n">
         <v>7</v>
@@ -4920,7 +4920,7 @@
         <v>850</v>
       </c>
       <c r="AC29" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="AD29" t="n">
         <v>30</v>
@@ -5216,7 +5216,7 @@
         <v>850</v>
       </c>
       <c r="Y31" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="Z31" t="n">
         <v>7</v>
@@ -5228,7 +5228,7 @@
         <v>850</v>
       </c>
       <c r="AC31" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="AD31" t="n">
         <v>30</v>
@@ -5524,7 +5524,7 @@
         <v>850</v>
       </c>
       <c r="Y33" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="Z33" t="n">
         <v>7</v>
@@ -5536,7 +5536,7 @@
         <v>850</v>
       </c>
       <c r="AC33" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="AD33" t="n">
         <v>30</v>
@@ -5832,7 +5832,7 @@
         <v>750</v>
       </c>
       <c r="Y35" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="Z35" t="n">
         <v>6</v>
@@ -5844,7 +5844,7 @@
         <v>750</v>
       </c>
       <c r="AC35" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="AD35" t="n">
         <v>30</v>
@@ -6140,7 +6140,7 @@
         <v>750</v>
       </c>
       <c r="Y37" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="Z37" t="n">
         <v>6</v>
@@ -6152,7 +6152,7 @@
         <v>750</v>
       </c>
       <c r="AC37" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="AD37" t="n">
         <v>30</v>
@@ -6448,7 +6448,7 @@
         <v>750</v>
       </c>
       <c r="Y39" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="Z39" t="n">
         <v>6</v>
@@ -6460,7 +6460,7 @@
         <v>750</v>
       </c>
       <c r="AC39" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="AD39" t="n">
         <v>30</v>
@@ -6756,7 +6756,7 @@
         <v>750</v>
       </c>
       <c r="Y41" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="Z41" t="n">
         <v>6</v>
@@ -6768,7 +6768,7 @@
         <v>750</v>
       </c>
       <c r="AC41" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="AD41" t="n">
         <v>30</v>
@@ -7064,7 +7064,7 @@
         <v>750</v>
       </c>
       <c r="Y43" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="Z43" t="n">
         <v>6</v>
@@ -7076,7 +7076,7 @@
         <v>750</v>
       </c>
       <c r="AC43" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="AD43" t="n">
         <v>30</v>
@@ -7372,7 +7372,7 @@
         <v>750</v>
       </c>
       <c r="Y45" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="Z45" t="n">
         <v>6</v>
@@ -7384,7 +7384,7 @@
         <v>750</v>
       </c>
       <c r="AC45" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="AD45" t="n">
         <v>30</v>
@@ -7680,7 +7680,7 @@
         <v>750</v>
       </c>
       <c r="Y47" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="Z47" t="n">
         <v>6</v>
@@ -7692,7 +7692,7 @@
         <v>750</v>
       </c>
       <c r="AC47" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="AD47" t="n">
         <v>30</v>
@@ -7988,7 +7988,7 @@
         <v>750</v>
       </c>
       <c r="Y49" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="Z49" t="n">
         <v>6</v>
@@ -8000,7 +8000,7 @@
         <v>750</v>
       </c>
       <c r="AC49" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="AD49" t="n">
         <v>30</v>
@@ -8296,7 +8296,7 @@
         <v>850</v>
       </c>
       <c r="Y51" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="Z51" t="n">
         <v>7</v>
@@ -8308,7 +8308,7 @@
         <v>850</v>
       </c>
       <c r="AC51" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="AD51" t="n">
         <v>30</v>
@@ -8604,7 +8604,7 @@
         <v>850</v>
       </c>
       <c r="Y53" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="Z53" t="n">
         <v>7</v>
@@ -8616,7 +8616,7 @@
         <v>850</v>
       </c>
       <c r="AC53" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="AD53" t="n">
         <v>30</v>
@@ -8912,7 +8912,7 @@
         <v>850</v>
       </c>
       <c r="Y55" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="Z55" t="n">
         <v>7</v>
@@ -8924,7 +8924,7 @@
         <v>850</v>
       </c>
       <c r="AC55" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="AD55" t="n">
         <v>30</v>
@@ -9220,7 +9220,7 @@
         <v>850</v>
       </c>
       <c r="Y57" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="Z57" t="n">
         <v>7</v>
@@ -9232,7 +9232,7 @@
         <v>850</v>
       </c>
       <c r="AC57" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="AD57" t="n">
         <v>30</v>
@@ -9528,7 +9528,7 @@
         <v>625</v>
       </c>
       <c r="Y59" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="Z59" t="n">
         <v>5</v>
@@ -9540,7 +9540,7 @@
         <v>625</v>
       </c>
       <c r="AC59" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="AD59" t="n">
         <v>30</v>
@@ -9836,7 +9836,7 @@
         <v>625</v>
       </c>
       <c r="Y61" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="Z61" t="n">
         <v>5</v>
@@ -9848,7 +9848,7 @@
         <v>625</v>
       </c>
       <c r="AC61" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="AD61" t="n">
         <v>30</v>
@@ -10144,7 +10144,7 @@
         <v>625</v>
       </c>
       <c r="Y63" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="Z63" t="n">
         <v>5</v>
@@ -10156,7 +10156,7 @@
         <v>625</v>
       </c>
       <c r="AC63" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="AD63" t="n">
         <v>30</v>
@@ -10452,7 +10452,7 @@
         <v>625</v>
       </c>
       <c r="Y65" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="Z65" t="n">
         <v>5</v>
@@ -10464,7 +10464,7 @@
         <v>625</v>
       </c>
       <c r="AC65" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="AD65" t="n">
         <v>30</v>
@@ -10760,7 +10760,7 @@
         <v>750</v>
       </c>
       <c r="Y67" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="Z67" t="n">
         <v>6</v>
@@ -10772,7 +10772,7 @@
         <v>750</v>
       </c>
       <c r="AC67" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="AD67" t="n">
         <v>30</v>
@@ -11068,7 +11068,7 @@
         <v>750</v>
       </c>
       <c r="Y69" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="Z69" t="n">
         <v>6</v>
@@ -11080,7 +11080,7 @@
         <v>750</v>
       </c>
       <c r="AC69" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="AD69" t="n">
         <v>30</v>
@@ -11376,7 +11376,7 @@
         <v>750</v>
       </c>
       <c r="Y71" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="Z71" t="n">
         <v>6</v>
@@ -11388,7 +11388,7 @@
         <v>750</v>
       </c>
       <c r="AC71" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="AD71" t="n">
         <v>30</v>
@@ -11684,7 +11684,7 @@
         <v>750</v>
       </c>
       <c r="Y73" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="Z73" t="n">
         <v>6</v>
@@ -11696,7 +11696,7 @@
         <v>750</v>
       </c>
       <c r="AC73" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="AD73" t="n">
         <v>30</v>
@@ -11992,7 +11992,7 @@
         <v>625</v>
       </c>
       <c r="Y75" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="Z75" t="n">
         <v>5</v>
@@ -12004,7 +12004,7 @@
         <v>625</v>
       </c>
       <c r="AC75" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="AD75" t="n">
         <v>30</v>
@@ -12300,7 +12300,7 @@
         <v>625</v>
       </c>
       <c r="Y77" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="Z77" t="n">
         <v>5</v>
@@ -12312,7 +12312,7 @@
         <v>625</v>
       </c>
       <c r="AC77" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="AD77" t="n">
         <v>30</v>
@@ -12608,7 +12608,7 @@
         <v>625</v>
       </c>
       <c r="Y79" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="Z79" t="n">
         <v>5</v>
@@ -12620,7 +12620,7 @@
         <v>625</v>
       </c>
       <c r="AC79" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="AD79" t="n">
         <v>30</v>
@@ -12916,7 +12916,7 @@
         <v>625</v>
       </c>
       <c r="Y81" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="Z81" t="n">
         <v>5</v>
@@ -12928,7 +12928,7 @@
         <v>625</v>
       </c>
       <c r="AC81" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="AD81" t="n">
         <v>30</v>
@@ -13224,7 +13224,7 @@
         <v>625</v>
       </c>
       <c r="Y83" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="Z83" t="n">
         <v>5</v>
@@ -13236,7 +13236,7 @@
         <v>625</v>
       </c>
       <c r="AC83" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="AD83" t="n">
         <v>30</v>
@@ -13532,7 +13532,7 @@
         <v>625</v>
       </c>
       <c r="Y85" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="Z85" t="n">
         <v>5</v>
@@ -13544,7 +13544,7 @@
         <v>625</v>
       </c>
       <c r="AC85" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="AD85" t="n">
         <v>30</v>
@@ -13840,7 +13840,7 @@
         <v>625</v>
       </c>
       <c r="Y87" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="Z87" t="n">
         <v>5</v>
@@ -13852,7 +13852,7 @@
         <v>625</v>
       </c>
       <c r="AC87" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="AD87" t="n">
         <v>30</v>
@@ -14148,7 +14148,7 @@
         <v>625</v>
       </c>
       <c r="Y89" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="Z89" t="n">
         <v>5</v>
@@ -14160,7 +14160,7 @@
         <v>625</v>
       </c>
       <c r="AC89" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="AD89" t="n">
         <v>30</v>
@@ -14456,7 +14456,7 @@
         <v>625</v>
       </c>
       <c r="Y91" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="Z91" t="n">
         <v>5</v>
@@ -14468,7 +14468,7 @@
         <v>625</v>
       </c>
       <c r="AC91" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="AD91" t="n">
         <v>30</v>
@@ -14764,7 +14764,7 @@
         <v>625</v>
       </c>
       <c r="Y93" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="Z93" t="n">
         <v>5</v>
@@ -14776,7 +14776,7 @@
         <v>625</v>
       </c>
       <c r="AC93" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="AD93" t="n">
         <v>30</v>
@@ -15072,7 +15072,7 @@
         <v>625</v>
       </c>
       <c r="Y95" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="Z95" t="n">
         <v>5</v>
@@ -15084,7 +15084,7 @@
         <v>625</v>
       </c>
       <c r="AC95" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="AD95" t="n">
         <v>30</v>
@@ -15380,7 +15380,7 @@
         <v>625</v>
       </c>
       <c r="Y97" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="Z97" t="n">
         <v>5</v>
@@ -15392,7 +15392,7 @@
         <v>625</v>
       </c>
       <c r="AC97" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="AD97" t="n">
         <v>30</v>
@@ -15688,7 +15688,7 @@
         <v>625</v>
       </c>
       <c r="Y99" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="Z99" t="n">
         <v>5</v>
@@ -15700,7 +15700,7 @@
         <v>625</v>
       </c>
       <c r="AC99" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="AD99" t="n">
         <v>30</v>
@@ -15996,7 +15996,7 @@
         <v>625</v>
       </c>
       <c r="Y101" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="Z101" t="n">
         <v>5</v>
@@ -16008,7 +16008,7 @@
         <v>625</v>
       </c>
       <c r="AC101" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="AD101" t="n">
         <v>30</v>
@@ -16304,7 +16304,7 @@
         <v>625</v>
       </c>
       <c r="Y103" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="Z103" t="n">
         <v>5</v>
@@ -16316,7 +16316,7 @@
         <v>625</v>
       </c>
       <c r="AC103" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="AD103" t="n">
         <v>30</v>
@@ -16612,7 +16612,7 @@
         <v>625</v>
       </c>
       <c r="Y105" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="Z105" t="n">
         <v>5</v>
@@ -16624,7 +16624,7 @@
         <v>625</v>
       </c>
       <c r="AC105" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="AD105" t="n">
         <v>30</v>
@@ -16920,7 +16920,7 @@
         <v>500</v>
       </c>
       <c r="Y107" t="n">
-        <v>25.97</v>
+        <v>20</v>
       </c>
       <c r="Z107" t="n">
         <v>4</v>
@@ -16932,7 +16932,7 @@
         <v>500</v>
       </c>
       <c r="AC107" t="n">
-        <v>25.97</v>
+        <v>20</v>
       </c>
       <c r="AD107" t="n">
         <v>30</v>
@@ -17228,7 +17228,7 @@
         <v>500</v>
       </c>
       <c r="Y109" t="n">
-        <v>25.97</v>
+        <v>20</v>
       </c>
       <c r="Z109" t="n">
         <v>4</v>
@@ -17240,7 +17240,7 @@
         <v>500</v>
       </c>
       <c r="AC109" t="n">
-        <v>25.97</v>
+        <v>20</v>
       </c>
       <c r="AD109" t="n">
         <v>30</v>
@@ -17536,7 +17536,7 @@
         <v>500</v>
       </c>
       <c r="Y111" t="n">
-        <v>25.97</v>
+        <v>20</v>
       </c>
       <c r="Z111" t="n">
         <v>4</v>
@@ -17548,7 +17548,7 @@
         <v>500</v>
       </c>
       <c r="AC111" t="n">
-        <v>25.97</v>
+        <v>20</v>
       </c>
       <c r="AD111" t="n">
         <v>30</v>
@@ -17844,7 +17844,7 @@
         <v>500</v>
       </c>
       <c r="Y113" t="n">
-        <v>25.97</v>
+        <v>20</v>
       </c>
       <c r="Z113" t="n">
         <v>4</v>
@@ -17856,7 +17856,7 @@
         <v>500</v>
       </c>
       <c r="AC113" t="n">
-        <v>25.97</v>
+        <v>20</v>
       </c>
       <c r="AD113" t="n">
         <v>30</v>
@@ -18152,7 +18152,7 @@
         <v>500</v>
       </c>
       <c r="Y115" t="n">
-        <v>25.97</v>
+        <v>20</v>
       </c>
       <c r="Z115" t="n">
         <v>4</v>
@@ -18164,7 +18164,7 @@
         <v>500</v>
       </c>
       <c r="AC115" t="n">
-        <v>25.97</v>
+        <v>20</v>
       </c>
       <c r="AD115" t="n">
         <v>30</v>
@@ -18460,7 +18460,7 @@
         <v>500</v>
       </c>
       <c r="Y117" t="n">
-        <v>25.97</v>
+        <v>20</v>
       </c>
       <c r="Z117" t="n">
         <v>4</v>
@@ -18472,7 +18472,7 @@
         <v>500</v>
       </c>
       <c r="AC117" t="n">
-        <v>25.97</v>
+        <v>20</v>
       </c>
       <c r="AD117" t="n">
         <v>30</v>
@@ -18768,7 +18768,7 @@
         <v>500</v>
       </c>
       <c r="Y119" t="n">
-        <v>25.97</v>
+        <v>20</v>
       </c>
       <c r="Z119" t="n">
         <v>4</v>
@@ -18780,7 +18780,7 @@
         <v>500</v>
       </c>
       <c r="AC119" t="n">
-        <v>25.97</v>
+        <v>20</v>
       </c>
       <c r="AD119" t="n">
         <v>30</v>
@@ -19076,7 +19076,7 @@
         <v>500</v>
       </c>
       <c r="Y121" t="n">
-        <v>25.97</v>
+        <v>20</v>
       </c>
       <c r="Z121" t="n">
         <v>4</v>
@@ -19088,7 +19088,7 @@
         <v>500</v>
       </c>
       <c r="AC121" t="n">
-        <v>25.97</v>
+        <v>20</v>
       </c>
       <c r="AD121" t="n">
         <v>30</v>
@@ -19384,7 +19384,7 @@
         <v>500</v>
       </c>
       <c r="Y123" t="n">
-        <v>25.97</v>
+        <v>20</v>
       </c>
       <c r="Z123" t="n">
         <v>4</v>
@@ -19396,7 +19396,7 @@
         <v>500</v>
       </c>
       <c r="AC123" t="n">
-        <v>25.97</v>
+        <v>20</v>
       </c>
       <c r="AD123" t="n">
         <v>30</v>
@@ -19692,7 +19692,7 @@
         <v>500</v>
       </c>
       <c r="Y125" t="n">
-        <v>25.97</v>
+        <v>20</v>
       </c>
       <c r="Z125" t="n">
         <v>4</v>
@@ -19704,7 +19704,7 @@
         <v>500</v>
       </c>
       <c r="AC125" t="n">
-        <v>25.97</v>
+        <v>20</v>
       </c>
       <c r="AD125" t="n">
         <v>30</v>
@@ -20000,7 +20000,7 @@
         <v>500</v>
       </c>
       <c r="Y127" t="n">
-        <v>25.97</v>
+        <v>20</v>
       </c>
       <c r="Z127" t="n">
         <v>4</v>
@@ -20012,7 +20012,7 @@
         <v>500</v>
       </c>
       <c r="AC127" t="n">
-        <v>25.97</v>
+        <v>20</v>
       </c>
       <c r="AD127" t="n">
         <v>30</v>
@@ -20308,7 +20308,7 @@
         <v>500</v>
       </c>
       <c r="Y129" t="n">
-        <v>25.97</v>
+        <v>20</v>
       </c>
       <c r="Z129" t="n">
         <v>4</v>
@@ -20320,7 +20320,7 @@
         <v>500</v>
       </c>
       <c r="AC129" t="n">
-        <v>25.97</v>
+        <v>20</v>
       </c>
       <c r="AD129" t="n">
         <v>30</v>
@@ -20616,7 +20616,7 @@
         <v>1000</v>
       </c>
       <c r="Y131" t="n">
-        <v>77.92</v>
+        <v>60</v>
       </c>
       <c r="Z131" t="n">
         <v>8</v>
@@ -20628,7 +20628,7 @@
         <v>1000</v>
       </c>
       <c r="AC131" t="n">
-        <v>77.92</v>
+        <v>60</v>
       </c>
       <c r="AD131" t="n">
         <v>30</v>
@@ -20924,7 +20924,7 @@
         <v>1000</v>
       </c>
       <c r="Y133" t="n">
-        <v>77.92</v>
+        <v>60</v>
       </c>
       <c r="Z133" t="n">
         <v>8</v>
@@ -20936,7 +20936,7 @@
         <v>1000</v>
       </c>
       <c r="AC133" t="n">
-        <v>77.92</v>
+        <v>60</v>
       </c>
       <c r="AD133" t="n">
         <v>30</v>
@@ -21232,7 +21232,7 @@
         <v>1000</v>
       </c>
       <c r="Y135" t="n">
-        <v>77.92</v>
+        <v>60</v>
       </c>
       <c r="Z135" t="n">
         <v>8</v>
@@ -21244,7 +21244,7 @@
         <v>1000</v>
       </c>
       <c r="AC135" t="n">
-        <v>77.92</v>
+        <v>60</v>
       </c>
       <c r="AD135" t="n">
         <v>30</v>
@@ -21540,7 +21540,7 @@
         <v>1000</v>
       </c>
       <c r="Y137" t="n">
-        <v>77.92</v>
+        <v>60</v>
       </c>
       <c r="Z137" t="n">
         <v>8</v>
@@ -21552,7 +21552,7 @@
         <v>1000</v>
       </c>
       <c r="AC137" t="n">
-        <v>77.92</v>
+        <v>60</v>
       </c>
       <c r="AD137" t="n">
         <v>30</v>
@@ -21848,7 +21848,7 @@
         <v>625</v>
       </c>
       <c r="Y139" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="Z139" t="n">
         <v>5</v>
@@ -21860,7 +21860,7 @@
         <v>625</v>
       </c>
       <c r="AC139" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="AD139" t="n">
         <v>30</v>
@@ -22156,7 +22156,7 @@
         <v>625</v>
       </c>
       <c r="Y141" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="Z141" t="n">
         <v>5</v>
@@ -22168,7 +22168,7 @@
         <v>625</v>
       </c>
       <c r="AC141" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="AD141" t="n">
         <v>30</v>
@@ -22464,7 +22464,7 @@
         <v>625</v>
       </c>
       <c r="Y143" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="Z143" t="n">
         <v>5</v>
@@ -22476,7 +22476,7 @@
         <v>625</v>
       </c>
       <c r="AC143" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="AD143" t="n">
         <v>30</v>
@@ -22772,7 +22772,7 @@
         <v>625</v>
       </c>
       <c r="Y145" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="Z145" t="n">
         <v>5</v>
@@ -22784,7 +22784,7 @@
         <v>625</v>
       </c>
       <c r="AC145" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="AD145" t="n">
         <v>30</v>
@@ -23080,7 +23080,7 @@
         <v>625</v>
       </c>
       <c r="Y147" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="Z147" t="n">
         <v>5</v>
@@ -23092,7 +23092,7 @@
         <v>625</v>
       </c>
       <c r="AC147" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="AD147" t="n">
         <v>30</v>
@@ -23388,7 +23388,7 @@
         <v>625</v>
       </c>
       <c r="Y149" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="Z149" t="n">
         <v>5</v>
@@ -23400,7 +23400,7 @@
         <v>625</v>
       </c>
       <c r="AC149" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="AD149" t="n">
         <v>30</v>
@@ -23696,7 +23696,7 @@
         <v>625</v>
       </c>
       <c r="Y151" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="Z151" t="n">
         <v>5</v>
@@ -23708,7 +23708,7 @@
         <v>625</v>
       </c>
       <c r="AC151" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="AD151" t="n">
         <v>30</v>
@@ -24004,7 +24004,7 @@
         <v>625</v>
       </c>
       <c r="Y153" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="Z153" t="n">
         <v>5</v>
@@ -24016,7 +24016,7 @@
         <v>625</v>
       </c>
       <c r="AC153" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="AD153" t="n">
         <v>30</v>
@@ -24312,7 +24312,7 @@
         <v>850</v>
       </c>
       <c r="Y155" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="Z155" t="n">
         <v>7</v>
@@ -24324,7 +24324,7 @@
         <v>850</v>
       </c>
       <c r="AC155" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="AD155" t="n">
         <v>30</v>
@@ -24620,7 +24620,7 @@
         <v>850</v>
       </c>
       <c r="Y157" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="Z157" t="n">
         <v>7</v>
@@ -24632,7 +24632,7 @@
         <v>850</v>
       </c>
       <c r="AC157" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="AD157" t="n">
         <v>30</v>
@@ -24928,7 +24928,7 @@
         <v>850</v>
       </c>
       <c r="Y159" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="Z159" t="n">
         <v>7</v>
@@ -24940,7 +24940,7 @@
         <v>850</v>
       </c>
       <c r="AC159" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="AD159" t="n">
         <v>30</v>
@@ -25236,7 +25236,7 @@
         <v>850</v>
       </c>
       <c r="Y161" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="Z161" t="n">
         <v>7</v>
@@ -25248,7 +25248,7 @@
         <v>850</v>
       </c>
       <c r="AC161" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="AD161" t="n">
         <v>30</v>
@@ -25544,7 +25544,7 @@
         <v>850</v>
       </c>
       <c r="Y163" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="Z163" t="n">
         <v>7</v>
@@ -25556,7 +25556,7 @@
         <v>850</v>
       </c>
       <c r="AC163" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="AD163" t="n">
         <v>30</v>
@@ -25852,7 +25852,7 @@
         <v>850</v>
       </c>
       <c r="Y165" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="Z165" t="n">
         <v>7</v>
@@ -25864,7 +25864,7 @@
         <v>850</v>
       </c>
       <c r="AC165" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="AD165" t="n">
         <v>30</v>
@@ -26160,7 +26160,7 @@
         <v>850</v>
       </c>
       <c r="Y167" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="Z167" t="n">
         <v>7</v>
@@ -26172,7 +26172,7 @@
         <v>850</v>
       </c>
       <c r="AC167" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="AD167" t="n">
         <v>30</v>
@@ -26468,7 +26468,7 @@
         <v>850</v>
       </c>
       <c r="Y169" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="Z169" t="n">
         <v>7</v>
@@ -26480,7 +26480,7 @@
         <v>850</v>
       </c>
       <c r="AC169" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="AD169" t="n">
         <v>30</v>
@@ -26776,7 +26776,7 @@
         <v>625</v>
       </c>
       <c r="Y171" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="Z171" t="n">
         <v>5</v>
@@ -26788,7 +26788,7 @@
         <v>625</v>
       </c>
       <c r="AC171" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="AD171" t="n">
         <v>30</v>
@@ -27084,7 +27084,7 @@
         <v>625</v>
       </c>
       <c r="Y173" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="Z173" t="n">
         <v>5</v>
@@ -27096,7 +27096,7 @@
         <v>625</v>
       </c>
       <c r="AC173" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="AD173" t="n">
         <v>30</v>
@@ -27392,7 +27392,7 @@
         <v>625</v>
       </c>
       <c r="Y175" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="Z175" t="n">
         <v>5</v>
@@ -27404,7 +27404,7 @@
         <v>625</v>
       </c>
       <c r="AC175" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="AD175" t="n">
         <v>30</v>
@@ -27700,7 +27700,7 @@
         <v>625</v>
       </c>
       <c r="Y177" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="Z177" t="n">
         <v>5</v>
@@ -27712,7 +27712,7 @@
         <v>625</v>
       </c>
       <c r="AC177" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="AD177" t="n">
         <v>30</v>
@@ -28008,7 +28008,7 @@
         <v>750</v>
       </c>
       <c r="Y179" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="Z179" t="n">
         <v>6</v>
@@ -28020,7 +28020,7 @@
         <v>750</v>
       </c>
       <c r="AC179" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="AD179" t="n">
         <v>30</v>
@@ -28316,7 +28316,7 @@
         <v>750</v>
       </c>
       <c r="Y181" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="Z181" t="n">
         <v>6</v>
@@ -28328,7 +28328,7 @@
         <v>750</v>
       </c>
       <c r="AC181" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="AD181" t="n">
         <v>30</v>
@@ -28624,7 +28624,7 @@
         <v>750</v>
       </c>
       <c r="Y183" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="Z183" t="n">
         <v>6</v>
@@ -28636,7 +28636,7 @@
         <v>750</v>
       </c>
       <c r="AC183" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="AD183" t="n">
         <v>30</v>
@@ -28932,7 +28932,7 @@
         <v>750</v>
       </c>
       <c r="Y185" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="Z185" t="n">
         <v>6</v>
@@ -28944,7 +28944,7 @@
         <v>750</v>
       </c>
       <c r="AC185" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="AD185" t="n">
         <v>30</v>
@@ -29240,7 +29240,7 @@
         <v>750</v>
       </c>
       <c r="Y187" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="Z187" t="n">
         <v>6</v>
@@ -29252,7 +29252,7 @@
         <v>750</v>
       </c>
       <c r="AC187" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="AD187" t="n">
         <v>30</v>
@@ -29548,7 +29548,7 @@
         <v>750</v>
       </c>
       <c r="Y189" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="Z189" t="n">
         <v>6</v>
@@ -29560,7 +29560,7 @@
         <v>750</v>
       </c>
       <c r="AC189" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="AD189" t="n">
         <v>30</v>
@@ -29856,7 +29856,7 @@
         <v>750</v>
       </c>
       <c r="Y191" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="Z191" t="n">
         <v>6</v>
@@ -29868,7 +29868,7 @@
         <v>750</v>
       </c>
       <c r="AC191" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="AD191" t="n">
         <v>30</v>
@@ -30164,7 +30164,7 @@
         <v>750</v>
       </c>
       <c r="Y193" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="Z193" t="n">
         <v>6</v>
@@ -30176,7 +30176,7 @@
         <v>750</v>
       </c>
       <c r="AC193" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="AD193" t="n">
         <v>30</v>
@@ -30472,7 +30472,7 @@
         <v>850</v>
       </c>
       <c r="Y195" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="Z195" t="n">
         <v>7</v>
@@ -30484,7 +30484,7 @@
         <v>850</v>
       </c>
       <c r="AC195" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="AD195" t="n">
         <v>30</v>
@@ -30780,7 +30780,7 @@
         <v>850</v>
       </c>
       <c r="Y197" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="Z197" t="n">
         <v>7</v>
@@ -30792,7 +30792,7 @@
         <v>850</v>
       </c>
       <c r="AC197" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="AD197" t="n">
         <v>30</v>
@@ -31088,7 +31088,7 @@
         <v>850</v>
       </c>
       <c r="Y199" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="Z199" t="n">
         <v>7</v>
@@ -31100,7 +31100,7 @@
         <v>850</v>
       </c>
       <c r="AC199" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="AD199" t="n">
         <v>30</v>
@@ -31396,7 +31396,7 @@
         <v>850</v>
       </c>
       <c r="Y201" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="Z201" t="n">
         <v>7</v>
@@ -31408,7 +31408,7 @@
         <v>850</v>
       </c>
       <c r="AC201" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="AD201" t="n">
         <v>30</v>
@@ -31704,7 +31704,7 @@
         <v>750</v>
       </c>
       <c r="Y203" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="Z203" t="n">
         <v>6</v>
@@ -31716,7 +31716,7 @@
         <v>750</v>
       </c>
       <c r="AC203" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="AD203" t="n">
         <v>30</v>
@@ -32012,7 +32012,7 @@
         <v>750</v>
       </c>
       <c r="Y205" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="Z205" t="n">
         <v>6</v>
@@ -32024,7 +32024,7 @@
         <v>750</v>
       </c>
       <c r="AC205" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="AD205" t="n">
         <v>30</v>
@@ -32320,7 +32320,7 @@
         <v>750</v>
       </c>
       <c r="Y207" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="Z207" t="n">
         <v>6</v>
@@ -32332,7 +32332,7 @@
         <v>750</v>
       </c>
       <c r="AC207" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="AD207" t="n">
         <v>30</v>
@@ -32628,7 +32628,7 @@
         <v>750</v>
       </c>
       <c r="Y209" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="Z209" t="n">
         <v>6</v>
@@ -32640,7 +32640,7 @@
         <v>750</v>
       </c>
       <c r="AC209" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="AD209" t="n">
         <v>30</v>
@@ -32936,7 +32936,7 @@
         <v>1000</v>
       </c>
       <c r="Y211" t="n">
-        <v>77.92</v>
+        <v>60</v>
       </c>
       <c r="Z211" t="n">
         <v>8</v>
@@ -32948,7 +32948,7 @@
         <v>1000</v>
       </c>
       <c r="AC211" t="n">
-        <v>77.92</v>
+        <v>60</v>
       </c>
       <c r="AD211" t="n">
         <v>30</v>
@@ -33244,7 +33244,7 @@
         <v>1000</v>
       </c>
       <c r="Y213" t="n">
-        <v>77.92</v>
+        <v>60</v>
       </c>
       <c r="Z213" t="n">
         <v>8</v>
@@ -33256,7 +33256,7 @@
         <v>1000</v>
       </c>
       <c r="AC213" t="n">
-        <v>77.92</v>
+        <v>60</v>
       </c>
       <c r="AD213" t="n">
         <v>30</v>
@@ -33552,7 +33552,7 @@
         <v>1000</v>
       </c>
       <c r="Y215" t="n">
-        <v>77.92</v>
+        <v>60</v>
       </c>
       <c r="Z215" t="n">
         <v>8</v>
@@ -33564,7 +33564,7 @@
         <v>1000</v>
       </c>
       <c r="AC215" t="n">
-        <v>77.92</v>
+        <v>60</v>
       </c>
       <c r="AD215" t="n">
         <v>30</v>
@@ -33860,7 +33860,7 @@
         <v>1000</v>
       </c>
       <c r="Y217" t="n">
-        <v>77.92</v>
+        <v>60</v>
       </c>
       <c r="Z217" t="n">
         <v>8</v>
@@ -33872,7 +33872,7 @@
         <v>1000</v>
       </c>
       <c r="AC217" t="n">
-        <v>77.92</v>
+        <v>60</v>
       </c>
       <c r="AD217" t="n">
         <v>30</v>
@@ -34168,7 +34168,7 @@
         <v>625</v>
       </c>
       <c r="Y219" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="Z219" t="n">
         <v>5</v>
@@ -34180,7 +34180,7 @@
         <v>625</v>
       </c>
       <c r="AC219" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="AD219" t="n">
         <v>30</v>
@@ -34476,7 +34476,7 @@
         <v>625</v>
       </c>
       <c r="Y221" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="Z221" t="n">
         <v>5</v>
@@ -34488,7 +34488,7 @@
         <v>625</v>
       </c>
       <c r="AC221" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="AD221" t="n">
         <v>30</v>
@@ -34784,7 +34784,7 @@
         <v>625</v>
       </c>
       <c r="Y223" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="Z223" t="n">
         <v>5</v>
@@ -34796,7 +34796,7 @@
         <v>625</v>
       </c>
       <c r="AC223" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="AD223" t="n">
         <v>30</v>
@@ -35092,7 +35092,7 @@
         <v>625</v>
       </c>
       <c r="Y225" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="Z225" t="n">
         <v>5</v>
@@ -35104,7 +35104,7 @@
         <v>625</v>
       </c>
       <c r="AC225" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="AD225" t="n">
         <v>30</v>
@@ -35400,7 +35400,7 @@
         <v>850</v>
       </c>
       <c r="Y227" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="Z227" t="n">
         <v>7</v>
@@ -35412,7 +35412,7 @@
         <v>850</v>
       </c>
       <c r="AC227" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="AD227" t="n">
         <v>30</v>
@@ -35708,7 +35708,7 @@
         <v>850</v>
       </c>
       <c r="Y229" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="Z229" t="n">
         <v>7</v>
@@ -35720,7 +35720,7 @@
         <v>850</v>
       </c>
       <c r="AC229" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="AD229" t="n">
         <v>30</v>
@@ -36016,7 +36016,7 @@
         <v>850</v>
       </c>
       <c r="Y231" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="Z231" t="n">
         <v>7</v>
@@ -36028,7 +36028,7 @@
         <v>850</v>
       </c>
       <c r="AC231" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="AD231" t="n">
         <v>30</v>
@@ -36324,7 +36324,7 @@
         <v>850</v>
       </c>
       <c r="Y233" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="Z233" t="n">
         <v>7</v>
@@ -36336,7 +36336,7 @@
         <v>850</v>
       </c>
       <c r="AC233" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="AD233" t="n">
         <v>30</v>
@@ -36632,7 +36632,7 @@
         <v>750</v>
       </c>
       <c r="Y235" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="Z235" t="n">
         <v>6</v>
@@ -36644,7 +36644,7 @@
         <v>750</v>
       </c>
       <c r="AC235" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="AD235" t="n">
         <v>30</v>
@@ -36940,7 +36940,7 @@
         <v>750</v>
       </c>
       <c r="Y237" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="Z237" t="n">
         <v>6</v>
@@ -36952,7 +36952,7 @@
         <v>750</v>
       </c>
       <c r="AC237" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="AD237" t="n">
         <v>30</v>
@@ -37248,7 +37248,7 @@
         <v>750</v>
       </c>
       <c r="Y239" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="Z239" t="n">
         <v>6</v>
@@ -37260,7 +37260,7 @@
         <v>750</v>
       </c>
       <c r="AC239" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="AD239" t="n">
         <v>30</v>
@@ -37556,7 +37556,7 @@
         <v>750</v>
       </c>
       <c r="Y241" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="Z241" t="n">
         <v>6</v>
@@ -37568,7 +37568,7 @@
         <v>750</v>
       </c>
       <c r="AC241" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="AD241" t="n">
         <v>30</v>
@@ -37864,7 +37864,7 @@
         <v>750</v>
       </c>
       <c r="Y243" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="Z243" t="n">
         <v>6</v>
@@ -37876,7 +37876,7 @@
         <v>750</v>
       </c>
       <c r="AC243" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="AD243" t="n">
         <v>30</v>
@@ -38172,7 +38172,7 @@
         <v>750</v>
       </c>
       <c r="Y245" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="Z245" t="n">
         <v>6</v>
@@ -38184,7 +38184,7 @@
         <v>750</v>
       </c>
       <c r="AC245" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="AD245" t="n">
         <v>30</v>
@@ -38480,7 +38480,7 @@
         <v>750</v>
       </c>
       <c r="Y247" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="Z247" t="n">
         <v>6</v>
@@ -38492,7 +38492,7 @@
         <v>750</v>
       </c>
       <c r="AC247" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="AD247" t="n">
         <v>30</v>
@@ -38788,7 +38788,7 @@
         <v>750</v>
       </c>
       <c r="Y249" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="Z249" t="n">
         <v>6</v>
@@ -38800,7 +38800,7 @@
         <v>750</v>
       </c>
       <c r="AC249" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="AD249" t="n">
         <v>30</v>
@@ -39096,7 +39096,7 @@
         <v>850</v>
       </c>
       <c r="Y251" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="Z251" t="n">
         <v>7</v>
@@ -39108,7 +39108,7 @@
         <v>850</v>
       </c>
       <c r="AC251" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="AD251" t="n">
         <v>30</v>
@@ -39404,7 +39404,7 @@
         <v>850</v>
       </c>
       <c r="Y253" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="Z253" t="n">
         <v>7</v>
@@ -39416,7 +39416,7 @@
         <v>850</v>
       </c>
       <c r="AC253" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="AD253" t="n">
         <v>30</v>
@@ -39712,7 +39712,7 @@
         <v>850</v>
       </c>
       <c r="Y255" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="Z255" t="n">
         <v>7</v>
@@ -39724,7 +39724,7 @@
         <v>850</v>
       </c>
       <c r="AC255" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="AD255" t="n">
         <v>30</v>
@@ -40020,7 +40020,7 @@
         <v>850</v>
       </c>
       <c r="Y257" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="Z257" t="n">
         <v>7</v>
@@ -40032,7 +40032,7 @@
         <v>850</v>
       </c>
       <c r="AC257" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="AD257" t="n">
         <v>30</v>
@@ -40328,7 +40328,7 @@
         <v>750</v>
       </c>
       <c r="Y259" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="Z259" t="n">
         <v>6</v>
@@ -40340,7 +40340,7 @@
         <v>750</v>
       </c>
       <c r="AC259" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="AD259" t="n">
         <v>30</v>
@@ -40636,7 +40636,7 @@
         <v>750</v>
       </c>
       <c r="Y261" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="Z261" t="n">
         <v>6</v>
@@ -40648,7 +40648,7 @@
         <v>750</v>
       </c>
       <c r="AC261" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="AD261" t="n">
         <v>30</v>
@@ -40944,7 +40944,7 @@
         <v>750</v>
       </c>
       <c r="Y263" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="Z263" t="n">
         <v>6</v>
@@ -40956,7 +40956,7 @@
         <v>750</v>
       </c>
       <c r="AC263" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="AD263" t="n">
         <v>30</v>
@@ -41252,7 +41252,7 @@
         <v>750</v>
       </c>
       <c r="Y265" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="Z265" t="n">
         <v>6</v>
@@ -41264,7 +41264,7 @@
         <v>750</v>
       </c>
       <c r="AC265" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="AD265" t="n">
         <v>30</v>
@@ -41560,7 +41560,7 @@
         <v>750</v>
       </c>
       <c r="Y267" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="Z267" t="n">
         <v>6</v>
@@ -41572,7 +41572,7 @@
         <v>750</v>
       </c>
       <c r="AC267" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="AD267" t="n">
         <v>30</v>
@@ -41868,7 +41868,7 @@
         <v>750</v>
       </c>
       <c r="Y269" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="Z269" t="n">
         <v>6</v>
@@ -41880,7 +41880,7 @@
         <v>750</v>
       </c>
       <c r="AC269" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="AD269" t="n">
         <v>30</v>
@@ -42176,7 +42176,7 @@
         <v>750</v>
       </c>
       <c r="Y271" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="Z271" t="n">
         <v>6</v>
@@ -42188,7 +42188,7 @@
         <v>750</v>
       </c>
       <c r="AC271" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="AD271" t="n">
         <v>30</v>
@@ -42484,7 +42484,7 @@
         <v>750</v>
       </c>
       <c r="Y273" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="Z273" t="n">
         <v>6</v>
@@ -42496,7 +42496,7 @@
         <v>750</v>
       </c>
       <c r="AC273" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="AD273" t="n">
         <v>30</v>
@@ -42792,7 +42792,7 @@
         <v>500</v>
       </c>
       <c r="Y275" t="n">
-        <v>25.97</v>
+        <v>20</v>
       </c>
       <c r="Z275" t="n">
         <v>4</v>
@@ -42804,7 +42804,7 @@
         <v>500</v>
       </c>
       <c r="AC275" t="n">
-        <v>25.97</v>
+        <v>20</v>
       </c>
       <c r="AD275" t="n">
         <v>30</v>
@@ -43100,7 +43100,7 @@
         <v>500</v>
       </c>
       <c r="Y277" t="n">
-        <v>25.97</v>
+        <v>20</v>
       </c>
       <c r="Z277" t="n">
         <v>4</v>
@@ -43112,7 +43112,7 @@
         <v>500</v>
       </c>
       <c r="AC277" t="n">
-        <v>25.97</v>
+        <v>20</v>
       </c>
       <c r="AD277" t="n">
         <v>30</v>
@@ -43408,7 +43408,7 @@
         <v>500</v>
       </c>
       <c r="Y279" t="n">
-        <v>25.97</v>
+        <v>20</v>
       </c>
       <c r="Z279" t="n">
         <v>4</v>
@@ -43420,7 +43420,7 @@
         <v>500</v>
       </c>
       <c r="AC279" t="n">
-        <v>25.97</v>
+        <v>20</v>
       </c>
       <c r="AD279" t="n">
         <v>30</v>
@@ -43716,7 +43716,7 @@
         <v>500</v>
       </c>
       <c r="Y281" t="n">
-        <v>25.97</v>
+        <v>20</v>
       </c>
       <c r="Z281" t="n">
         <v>4</v>
@@ -43728,7 +43728,7 @@
         <v>500</v>
       </c>
       <c r="AC281" t="n">
-        <v>25.97</v>
+        <v>20</v>
       </c>
       <c r="AD281" t="n">
         <v>30</v>
@@ -44024,7 +44024,7 @@
         <v>750</v>
       </c>
       <c r="Y283" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="Z283" t="n">
         <v>6</v>
@@ -44036,7 +44036,7 @@
         <v>750</v>
       </c>
       <c r="AC283" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="AD283" t="n">
         <v>30</v>
@@ -44332,7 +44332,7 @@
         <v>750</v>
       </c>
       <c r="Y285" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="Z285" t="n">
         <v>6</v>
@@ -44344,7 +44344,7 @@
         <v>750</v>
       </c>
       <c r="AC285" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="AD285" t="n">
         <v>30</v>
@@ -44640,7 +44640,7 @@
         <v>750</v>
       </c>
       <c r="Y287" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="Z287" t="n">
         <v>6</v>
@@ -44652,7 +44652,7 @@
         <v>750</v>
       </c>
       <c r="AC287" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="AD287" t="n">
         <v>30</v>
@@ -44948,7 +44948,7 @@
         <v>750</v>
       </c>
       <c r="Y289" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="Z289" t="n">
         <v>6</v>
@@ -44960,7 +44960,7 @@
         <v>750</v>
       </c>
       <c r="AC289" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="AD289" t="n">
         <v>30</v>
@@ -45256,7 +45256,7 @@
         <v>1000</v>
       </c>
       <c r="Y291" t="n">
-        <v>77.92</v>
+        <v>60</v>
       </c>
       <c r="Z291" t="n">
         <v>8</v>
@@ -45268,7 +45268,7 @@
         <v>1000</v>
       </c>
       <c r="AC291" t="n">
-        <v>77.92</v>
+        <v>60</v>
       </c>
       <c r="AD291" t="n">
         <v>30</v>
@@ -45564,7 +45564,7 @@
         <v>1000</v>
       </c>
       <c r="Y293" t="n">
-        <v>77.92</v>
+        <v>60</v>
       </c>
       <c r="Z293" t="n">
         <v>8</v>
@@ -45576,7 +45576,7 @@
         <v>1000</v>
       </c>
       <c r="AC293" t="n">
-        <v>77.92</v>
+        <v>60</v>
       </c>
       <c r="AD293" t="n">
         <v>30</v>
@@ -45872,7 +45872,7 @@
         <v>1000</v>
       </c>
       <c r="Y295" t="n">
-        <v>77.92</v>
+        <v>60</v>
       </c>
       <c r="Z295" t="n">
         <v>8</v>
@@ -45884,7 +45884,7 @@
         <v>1000</v>
       </c>
       <c r="AC295" t="n">
-        <v>77.92</v>
+        <v>60</v>
       </c>
       <c r="AD295" t="n">
         <v>30</v>
@@ -46180,7 +46180,7 @@
         <v>1000</v>
       </c>
       <c r="Y297" t="n">
-        <v>77.92</v>
+        <v>60</v>
       </c>
       <c r="Z297" t="n">
         <v>8</v>
@@ -46192,7 +46192,7 @@
         <v>1000</v>
       </c>
       <c r="AC297" t="n">
-        <v>77.92</v>
+        <v>60</v>
       </c>
       <c r="AD297" t="n">
         <v>30</v>
@@ -46488,7 +46488,7 @@
         <v>1000</v>
       </c>
       <c r="Y299" t="n">
-        <v>77.92</v>
+        <v>60</v>
       </c>
       <c r="Z299" t="n">
         <v>8</v>
@@ -46500,7 +46500,7 @@
         <v>1000</v>
       </c>
       <c r="AC299" t="n">
-        <v>77.92</v>
+        <v>60</v>
       </c>
       <c r="AD299" t="n">
         <v>30</v>
@@ -46796,7 +46796,7 @@
         <v>1000</v>
       </c>
       <c r="Y301" t="n">
-        <v>77.92</v>
+        <v>60</v>
       </c>
       <c r="Z301" t="n">
         <v>8</v>
@@ -46808,7 +46808,7 @@
         <v>1000</v>
       </c>
       <c r="AC301" t="n">
-        <v>77.92</v>
+        <v>60</v>
       </c>
       <c r="AD301" t="n">
         <v>30</v>
@@ -47104,7 +47104,7 @@
         <v>1000</v>
       </c>
       <c r="Y303" t="n">
-        <v>77.92</v>
+        <v>60</v>
       </c>
       <c r="Z303" t="n">
         <v>8</v>
@@ -47116,7 +47116,7 @@
         <v>1000</v>
       </c>
       <c r="AC303" t="n">
-        <v>77.92</v>
+        <v>60</v>
       </c>
       <c r="AD303" t="n">
         <v>30</v>
@@ -47412,7 +47412,7 @@
         <v>1000</v>
       </c>
       <c r="Y305" t="n">
-        <v>77.92</v>
+        <v>60</v>
       </c>
       <c r="Z305" t="n">
         <v>8</v>
@@ -47424,7 +47424,7 @@
         <v>1000</v>
       </c>
       <c r="AC305" t="n">
-        <v>77.92</v>
+        <v>60</v>
       </c>
       <c r="AD305" t="n">
         <v>30</v>
@@ -47720,7 +47720,7 @@
         <v>850</v>
       </c>
       <c r="Y307" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="Z307" t="n">
         <v>7</v>
@@ -47732,7 +47732,7 @@
         <v>850</v>
       </c>
       <c r="AC307" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="AD307" t="n">
         <v>30</v>
@@ -48028,7 +48028,7 @@
         <v>850</v>
       </c>
       <c r="Y309" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="Z309" t="n">
         <v>7</v>
@@ -48040,7 +48040,7 @@
         <v>850</v>
       </c>
       <c r="AC309" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="AD309" t="n">
         <v>30</v>
@@ -48336,7 +48336,7 @@
         <v>850</v>
       </c>
       <c r="Y311" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="Z311" t="n">
         <v>7</v>
@@ -48348,7 +48348,7 @@
         <v>850</v>
       </c>
       <c r="AC311" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="AD311" t="n">
         <v>30</v>
@@ -48644,7 +48644,7 @@
         <v>850</v>
       </c>
       <c r="Y313" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="Z313" t="n">
         <v>7</v>
@@ -48656,7 +48656,7 @@
         <v>850</v>
       </c>
       <c r="AC313" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="AD313" t="n">
         <v>30</v>
@@ -48952,7 +48952,7 @@
         <v>625</v>
       </c>
       <c r="Y315" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="Z315" t="n">
         <v>5</v>
@@ -48964,7 +48964,7 @@
         <v>625</v>
       </c>
       <c r="AC315" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="AD315" t="n">
         <v>30</v>
@@ -49260,7 +49260,7 @@
         <v>625</v>
       </c>
       <c r="Y317" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="Z317" t="n">
         <v>5</v>
@@ -49272,7 +49272,7 @@
         <v>625</v>
       </c>
       <c r="AC317" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="AD317" t="n">
         <v>30</v>
@@ -49568,7 +49568,7 @@
         <v>625</v>
       </c>
       <c r="Y319" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="Z319" t="n">
         <v>5</v>
@@ -49580,7 +49580,7 @@
         <v>625</v>
       </c>
       <c r="AC319" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="AD319" t="n">
         <v>30</v>
@@ -49876,7 +49876,7 @@
         <v>625</v>
       </c>
       <c r="Y321" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="Z321" t="n">
         <v>5</v>
@@ -49888,7 +49888,7 @@
         <v>625</v>
       </c>
       <c r="AC321" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="AD321" t="n">
         <v>30</v>
